--- a/data/FRS_filtered/Dec/Fmn G Dec/Dec 2025 G.xlsx
+++ b/data/FRS_filtered/Dec/Fmn G Dec/Dec 2025 G.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{584D06FC-FCF5-4EDA-8481-4B2E1A64BC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC447E4-857D-4DF3-ABF3-C26B719936B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="84" windowWidth="23040" windowHeight="12156" tabRatio="811" activeTab="1" xr2:uid="{32212EA4-CB97-4EFB-BF0B-A0135F8E7177}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12156" tabRatio="811" activeTab="1" xr2:uid="{32212EA4-CB97-4EFB-BF0B-A0135F8E7177}"/>
   </bookViews>
   <sheets>
     <sheet name="B Veh" sheetId="14" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'B Veh'!#REF!</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'C Veh'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Armt!$A$1:$T$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'B Veh'!$A$1:$T$17</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'C Veh'!$A$1:$T$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'B Veh'!$A$1:$P$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'C Veh'!$A$1:$P$19</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">Inst!$A$1:$P$124</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">SA!$A$1:$Q$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'B Veh'!$2:$4</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="223">
   <si>
     <t>Ser</t>
   </si>
@@ -1032,7 +1032,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1266,9 +1266,6 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1458,9 +1455,6 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
@@ -1486,18 +1480,24 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1507,12 +1507,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1522,11 +1516,62 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1536,57 +1581,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1981,7 +1975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D38722E-13BF-436B-9700-850B17CFB5EC}">
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="6" customWidth="1"/>
@@ -1998,90 +1992,71 @@
     <col min="13" max="13" width="8.88671875" style="6" customWidth="1"/>
     <col min="14" max="14" width="9.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="7.5546875" style="6" customWidth="1"/>
-    <col min="16" max="16" width="10.88671875" style="10" customWidth="1"/>
-    <col min="17" max="18" width="12" style="10" customWidth="1"/>
-    <col min="19" max="19" width="10.88671875" style="10" customWidth="1"/>
-    <col min="20" max="20" width="44.109375" style="11" customWidth="1"/>
-    <col min="21" max="16384" width="9.109375" style="10"/>
+    <col min="16" max="16" width="44.109375" style="11" customWidth="1"/>
+    <col min="17" max="16384" width="9.109375" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="143" t="s">
+    <row r="1" spans="1:16" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="142" t="s">
         <v>221</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
-      <c r="K1" s="143"/>
-      <c r="L1" s="143"/>
-      <c r="M1" s="143"/>
-      <c r="N1" s="143"/>
-      <c r="O1" s="143"/>
-      <c r="P1" s="143"/>
-      <c r="Q1" s="143"/>
-      <c r="R1" s="143"/>
-      <c r="S1" s="143"/>
-      <c r="T1" s="143"/>
-    </row>
-    <row r="2" spans="1:20" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="144" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="145" t="s">
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="142"/>
+      <c r="K1" s="142"/>
+      <c r="L1" s="142"/>
+      <c r="M1" s="142"/>
+      <c r="N1" s="142"/>
+      <c r="O1" s="142"/>
+      <c r="P1" s="142"/>
+    </row>
+    <row r="2" spans="1:16" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="143" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="141" t="s">
         <v>143</v>
       </c>
-      <c r="C2" s="144" t="s">
+      <c r="C2" s="143" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144" t="s">
+      <c r="D2" s="143"/>
+      <c r="E2" s="143" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="145" t="s">
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
+      <c r="K2" s="143"/>
+      <c r="L2" s="143"/>
+      <c r="M2" s="141" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="145" t="s">
+      <c r="N2" s="141" t="s">
         <v>46</v>
       </c>
-      <c r="O2" s="146" t="s">
+      <c r="O2" s="144" t="s">
         <v>47</v>
       </c>
-      <c r="P2" s="145" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q2" s="145" t="s">
-        <v>23</v>
-      </c>
-      <c r="R2" s="145" t="s">
-        <v>24</v>
-      </c>
-      <c r="S2" s="145" t="s">
-        <v>25</v>
-      </c>
-      <c r="T2" s="145" t="s">
+      <c r="P2" s="141" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:20" s="5" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="144"/>
-      <c r="B3" s="145"/>
+    <row r="3" spans="1:16" s="5" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="143"/>
+      <c r="B3" s="141"/>
       <c r="C3" s="72" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="87" t="s">
+      <c r="D3" s="86" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="71" t="s">
@@ -2108,16 +2083,12 @@
       <c r="L3" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="145"/>
-      <c r="N3" s="145"/>
-      <c r="O3" s="146"/>
-      <c r="P3" s="145"/>
-      <c r="Q3" s="145"/>
-      <c r="R3" s="145"/>
-      <c r="S3" s="145"/>
-      <c r="T3" s="145"/>
-    </row>
-    <row r="4" spans="1:20" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M3" s="141"/>
+      <c r="N3" s="141"/>
+      <c r="O3" s="144"/>
+      <c r="P3" s="141"/>
+    </row>
+    <row r="4" spans="1:16" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="71" t="s">
         <v>1</v>
       </c>
@@ -2163,30 +2134,18 @@
       <c r="O4" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="P4" s="71" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q4" s="71" t="s">
-        <v>55</v>
-      </c>
-      <c r="R4" s="71" t="s">
-        <v>56</v>
-      </c>
-      <c r="S4" s="71" t="s">
-        <v>57</v>
-      </c>
-      <c r="T4" s="92" t="s">
+      <c r="P4" s="91" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:20" s="83" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="82">
-        <v>1</v>
-      </c>
-      <c r="B5" s="84" t="s">
+    <row r="5" spans="1:16" s="82" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="81">
+        <v>1</v>
+      </c>
+      <c r="B5" s="83" t="s">
         <v>173</v>
       </c>
-      <c r="C5" s="112">
+      <c r="C5" s="111">
         <v>19</v>
       </c>
       <c r="D5" s="30">
@@ -2224,30 +2183,14 @@
         <v>0</v>
       </c>
       <c r="O5" s="25">
-        <f t="shared" ref="O5:O14" si="0">D5-M5</f>
+        <f>D5-M5</f>
         <v>12</v>
       </c>
-      <c r="P5" s="86">
-        <f t="shared" ref="P5:P14" si="1">IF(D5=0,"-",(M5/D5))</f>
-        <v>7.6923076923076927E-2</v>
-      </c>
-      <c r="Q5" s="86">
-        <f t="shared" ref="Q5:Q14" si="2">IF(D5=0,"-",(N5/D5))</f>
-        <v>0</v>
-      </c>
-      <c r="R5" s="86">
-        <f t="shared" ref="R5:R14" si="3">IF(D5=0,"-",(O5/D5))</f>
-        <v>0.92307692307692313</v>
-      </c>
-      <c r="S5" s="86">
-        <f t="shared" ref="S5:S14" si="4">IF(D5=0,"-",(Q5+R5))</f>
-        <v>0.92307692307692313</v>
-      </c>
-      <c r="T5" s="114" t="s">
+      <c r="P5" s="113" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="27" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" s="27" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>2</v>
       </c>
@@ -2284,37 +2227,21 @@
       <c r="L6" s="25">
         <v>0</v>
       </c>
-      <c r="M6" s="98">
+      <c r="M6" s="97">
         <v>1</v>
       </c>
       <c r="N6" s="25">
         <v>0</v>
       </c>
       <c r="O6" s="25">
-        <f t="shared" si="0"/>
+        <f>D6-M6</f>
         <v>44</v>
       </c>
-      <c r="P6" s="8">
-        <f t="shared" si="1"/>
-        <v>2.2222222222222223E-2</v>
-      </c>
-      <c r="Q6" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R6" s="8">
-        <f t="shared" si="3"/>
-        <v>0.97777777777777775</v>
-      </c>
-      <c r="S6" s="8">
-        <f t="shared" si="4"/>
-        <v>0.97777777777777775</v>
-      </c>
-      <c r="T6" s="97" t="s">
+      <c r="P6" s="96" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="7" spans="1:20" s="27" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" s="27" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>3</v>
       </c>
@@ -2358,29 +2285,13 @@
         <v>0</v>
       </c>
       <c r="O7" s="25">
-        <f t="shared" si="0"/>
+        <f>D7-M7</f>
         <v>30</v>
       </c>
-      <c r="P7" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q7" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R7" s="8">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="S7" s="8">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="T7" s="97"/>
-    </row>
-    <row r="8" spans="1:20" s="27" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="82">
+      <c r="P7" s="96"/>
+    </row>
+    <row r="8" spans="1:16" s="27" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="81">
         <v>4</v>
       </c>
       <c r="B8" s="24" t="s">
@@ -2416,7 +2327,7 @@
       <c r="L8" s="7">
         <v>0</v>
       </c>
-      <c r="M8" s="82">
+      <c r="M8" s="81">
         <f>E8+F8+G8+H8+I8+J8+K8+L8</f>
         <v>0</v>
       </c>
@@ -2424,30 +2335,14 @@
         <v>0</v>
       </c>
       <c r="O8" s="25">
-        <f t="shared" si="0"/>
+        <f>D8-M8</f>
         <v>3</v>
       </c>
-      <c r="P8" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R8" s="8">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="S8" s="8">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="T8" s="29" t="s">
+      <c r="P8" s="29" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="1:20" s="56" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" s="56" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>5</v>
       </c>
@@ -2484,37 +2379,21 @@
       <c r="L9" s="25">
         <v>0</v>
       </c>
-      <c r="M9" s="82">
+      <c r="M9" s="81">
         <v>0</v>
       </c>
       <c r="N9" s="25">
         <v>0</v>
       </c>
       <c r="O9" s="25">
-        <f t="shared" si="0"/>
+        <f>D9-M9</f>
         <v>29</v>
       </c>
-      <c r="P9" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R9" s="8">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="S9" s="8">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="T9" s="97" t="s">
+      <c r="P9" s="96" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="10" spans="1:20" s="27" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" s="27" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>6</v>
       </c>
@@ -2551,42 +2430,26 @@
       <c r="L10" s="7">
         <v>0</v>
       </c>
-      <c r="M10" s="82">
-        <f t="shared" ref="M10:M17" si="5">E10+F10+G10+H10+I10+J10+K10+L10</f>
+      <c r="M10" s="81">
+        <f>E10+F10+G10+H10+I10+J10+K10+L10</f>
         <v>0</v>
       </c>
       <c r="N10" s="7">
         <v>0</v>
       </c>
       <c r="O10" s="25">
-        <f t="shared" si="0"/>
+        <f>D10-M10</f>
         <v>2</v>
       </c>
-      <c r="P10" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q10" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R10" s="8">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="S10" s="8">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="T10" s="29" t="s">
+      <c r="P10" s="29" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="11" spans="1:20" s="69" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="82">
+    <row r="11" spans="1:16" s="69" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="81">
         <v>7</v>
       </c>
-      <c r="B11" s="90" t="s">
+      <c r="B11" s="89" t="s">
         <v>180</v>
       </c>
       <c r="C11" s="25" t="s">
@@ -2619,43 +2482,27 @@
       <c r="L11" s="25">
         <v>0</v>
       </c>
-      <c r="M11" s="82">
-        <f t="shared" si="5"/>
+      <c r="M11" s="81">
+        <f>E11+F11+G11+H11+I11+J11+K11+L11</f>
         <v>0</v>
       </c>
       <c r="N11" s="25">
         <v>0</v>
       </c>
       <c r="O11" s="25">
-        <f t="shared" si="0"/>
+        <f>D11-M11</f>
         <v>7</v>
       </c>
-      <c r="P11" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R11" s="8">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="S11" s="8">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="T11" s="81"/>
-    </row>
-    <row r="12" spans="1:20" s="56" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="P11" s="80"/>
+    </row>
+    <row r="12" spans="1:16" s="56" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>8</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="C12" s="78">
+      <c r="C12" s="77">
         <v>6</v>
       </c>
       <c r="D12" s="25">
@@ -2685,43 +2532,27 @@
       <c r="L12" s="25">
         <v>0</v>
       </c>
-      <c r="M12" s="82">
-        <f t="shared" si="5"/>
+      <c r="M12" s="81">
+        <f>E12+F12+G12+H12+I12+J12+K12+L12</f>
         <v>0</v>
       </c>
       <c r="N12" s="25">
         <v>0</v>
       </c>
       <c r="O12" s="25">
-        <f t="shared" si="0"/>
+        <f>D12-M12</f>
         <v>3</v>
       </c>
-      <c r="P12" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R12" s="8">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="S12" s="8">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="T12" s="80"/>
-    </row>
-    <row r="13" spans="1:20" s="56" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="P12" s="79"/>
+    </row>
+    <row r="13" spans="1:16" s="56" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>9</v>
       </c>
       <c r="B13" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="C13" s="142"/>
+      <c r="C13" s="140"/>
       <c r="D13" s="25">
         <v>3</v>
       </c>
@@ -2749,43 +2580,27 @@
       <c r="L13" s="25">
         <v>0</v>
       </c>
-      <c r="M13" s="82">
-        <f t="shared" si="5"/>
+      <c r="M13" s="81">
+        <f>E13+F13+G13+H13+I13+J13+K13+L13</f>
         <v>0</v>
       </c>
       <c r="N13" s="25">
         <v>0</v>
       </c>
       <c r="O13" s="25">
-        <f t="shared" si="0"/>
+        <f>D13-M13</f>
         <v>3</v>
       </c>
-      <c r="P13" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R13" s="8">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="S13" s="8">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="T13" s="80"/>
-    </row>
-    <row r="14" spans="1:20" s="56" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="82">
+      <c r="P13" s="79"/>
+    </row>
+    <row r="14" spans="1:16" s="56" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="81">
         <v>10</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="C14" s="141">
+      <c r="C14" s="139">
         <v>3</v>
       </c>
       <c r="D14" s="25">
@@ -2815,102 +2630,74 @@
       <c r="L14" s="25">
         <v>0</v>
       </c>
-      <c r="M14" s="82">
-        <f t="shared" si="5"/>
+      <c r="M14" s="81">
+        <f>E14+F14+G14+H14+I14+J14+K14+L14</f>
         <v>0</v>
       </c>
       <c r="N14" s="25">
         <v>0</v>
       </c>
       <c r="O14" s="25">
-        <f t="shared" si="0"/>
+        <f>D14-M14</f>
         <v>5</v>
       </c>
-      <c r="P14" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R14" s="8">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="S14" s="8">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="T14" s="97"/>
-    </row>
-    <row r="15" spans="1:20" s="26" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="P14" s="96"/>
+    </row>
+    <row r="15" spans="1:16" s="26" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>11</v>
       </c>
-      <c r="B15" s="84" t="s">
+      <c r="B15" s="83" t="s">
         <v>175</v>
       </c>
-      <c r="C15" s="110"/>
-      <c r="D15" s="85">
+      <c r="C15" s="109"/>
+      <c r="D15" s="84">
         <v>2</v>
       </c>
-      <c r="E15" s="85">
-        <v>0</v>
-      </c>
-      <c r="F15" s="85">
-        <v>0</v>
-      </c>
-      <c r="G15" s="85">
-        <v>0</v>
-      </c>
-      <c r="H15" s="85">
-        <v>0</v>
-      </c>
-      <c r="I15" s="85">
-        <v>0</v>
-      </c>
-      <c r="J15" s="85">
-        <v>0</v>
-      </c>
-      <c r="K15" s="85">
-        <v>0</v>
-      </c>
-      <c r="L15" s="85">
+      <c r="E15" s="84">
+        <v>0</v>
+      </c>
+      <c r="F15" s="84">
+        <v>0</v>
+      </c>
+      <c r="G15" s="84">
+        <v>0</v>
+      </c>
+      <c r="H15" s="84">
+        <v>0</v>
+      </c>
+      <c r="I15" s="84">
+        <v>0</v>
+      </c>
+      <c r="J15" s="84">
+        <v>0</v>
+      </c>
+      <c r="K15" s="84">
+        <v>0</v>
+      </c>
+      <c r="L15" s="84">
         <v>0</v>
       </c>
       <c r="M15" s="30">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N15" s="85">
+        <f>E15+F15+G15+H15+I15+J15+K15+L15</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="84">
         <v>0</v>
       </c>
       <c r="O15" s="25">
         <v>2</v>
       </c>
-      <c r="P15" s="86">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="86">
-        <v>0</v>
-      </c>
-      <c r="R15" s="86">
-        <v>1</v>
-      </c>
-      <c r="S15" s="86">
-        <v>1</v>
-      </c>
-      <c r="T15" s="94"/>
-    </row>
-    <row r="16" spans="1:20" s="56" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="P15" s="93"/>
+    </row>
+    <row r="16" spans="1:16" s="56" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>12</v>
       </c>
       <c r="B16" s="24" t="s">
         <v>174</v>
       </c>
-      <c r="C16" s="109"/>
+      <c r="C16" s="108"/>
       <c r="D16" s="25">
         <v>1</v>
       </c>
@@ -2939,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="30">
-        <f t="shared" si="5"/>
+        <f>E16+F16+G16+H16+I16+J16+K16+L16</f>
         <v>0</v>
       </c>
       <c r="N16" s="25">
@@ -2949,26 +2736,10 @@
         <f>D16-M16</f>
         <v>1</v>
       </c>
-      <c r="P16" s="8">
-        <f>IF(D16=0,"-",(M16/D16))</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="8">
-        <f>IF(D16=0,"-",(N16/D16))</f>
-        <v>0</v>
-      </c>
-      <c r="R16" s="8">
-        <f>IF(D16=0,"-",(O16/D16))</f>
-        <v>1</v>
-      </c>
-      <c r="S16" s="8">
-        <f>IF(D16=0,"-",(Q16+R16))</f>
-        <v>1</v>
-      </c>
-      <c r="T16" s="80"/>
-    </row>
-    <row r="17" spans="1:20" s="56" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="82">
+      <c r="P16" s="79"/>
+    </row>
+    <row r="17" spans="1:16" s="56" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="81">
         <v>13</v>
       </c>
       <c r="B17" s="24" t="s">
@@ -3004,8 +2775,8 @@
       <c r="L17" s="25">
         <v>0</v>
       </c>
-      <c r="M17" s="82">
-        <f t="shared" si="5"/>
+      <c r="M17" s="81">
+        <f>E17+F17+G17+H17+I17+J17+K17+L17</f>
         <v>0</v>
       </c>
       <c r="N17" s="25">
@@ -3015,30 +2786,12 @@
         <f>D17-M17</f>
         <v>2</v>
       </c>
-      <c r="P17" s="8">
-        <f>IF(D17=0,"-",(M17/D17))</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="8">
-        <f>IF(D17=0,"-",(N17/D17))</f>
-        <v>0</v>
-      </c>
-      <c r="R17" s="8">
-        <f>IF(D17=0,"-",(O17/D17))</f>
-        <v>1</v>
-      </c>
-      <c r="S17" s="8">
-        <f>IF(D17=0,"-",(Q17+R17))</f>
-        <v>1</v>
-      </c>
-      <c r="T17" s="80"/>
+      <c r="P17" s="79"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="A1:T1"/>
+  <mergeCells count="9">
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:D2"/>
@@ -3046,8 +2799,6 @@
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="Q2:Q3"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value Between 0 to 200000" sqref="O65223:O65484" xr:uid="{04F48C0D-740C-47D8-94F4-92D3462D3DF3}">
@@ -3066,7 +2817,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12BAABA0-718C-417E-B39E-FB21188BD679}">
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="6" customWidth="1"/>
@@ -3083,90 +2834,71 @@
     <col min="13" max="13" width="8.88671875" style="6" customWidth="1"/>
     <col min="14" max="14" width="9.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="7.5546875" style="6" customWidth="1"/>
-    <col min="16" max="16" width="10.88671875" style="10" customWidth="1"/>
-    <col min="17" max="18" width="12" style="10" customWidth="1"/>
-    <col min="19" max="19" width="10.88671875" style="10" customWidth="1"/>
-    <col min="20" max="20" width="44.109375" style="11" customWidth="1"/>
-    <col min="21" max="16384" width="9.109375" style="10"/>
+    <col min="16" max="16" width="44.109375" style="11" customWidth="1"/>
+    <col min="17" max="16384" width="9.109375" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="143" t="s">
+    <row r="1" spans="1:16" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="142" t="s">
         <v>222</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
-      <c r="K1" s="143"/>
-      <c r="L1" s="143"/>
-      <c r="M1" s="143"/>
-      <c r="N1" s="143"/>
-      <c r="O1" s="143"/>
-      <c r="P1" s="143"/>
-      <c r="Q1" s="143"/>
-      <c r="R1" s="143"/>
-      <c r="S1" s="143"/>
-      <c r="T1" s="143"/>
-    </row>
-    <row r="2" spans="1:20" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="144" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="145" t="s">
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="142"/>
+      <c r="K1" s="142"/>
+      <c r="L1" s="142"/>
+      <c r="M1" s="142"/>
+      <c r="N1" s="142"/>
+      <c r="O1" s="142"/>
+      <c r="P1" s="142"/>
+    </row>
+    <row r="2" spans="1:16" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="143" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="141" t="s">
         <v>143</v>
       </c>
-      <c r="C2" s="144" t="s">
+      <c r="C2" s="143" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144" t="s">
+      <c r="D2" s="143"/>
+      <c r="E2" s="143" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="145" t="s">
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
+      <c r="K2" s="143"/>
+      <c r="L2" s="143"/>
+      <c r="M2" s="141" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="145" t="s">
+      <c r="N2" s="141" t="s">
         <v>46</v>
       </c>
-      <c r="O2" s="146" t="s">
+      <c r="O2" s="144" t="s">
         <v>47</v>
       </c>
-      <c r="P2" s="145" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q2" s="145" t="s">
-        <v>23</v>
-      </c>
-      <c r="R2" s="145" t="s">
-        <v>24</v>
-      </c>
-      <c r="S2" s="145" t="s">
-        <v>25</v>
-      </c>
-      <c r="T2" s="145" t="s">
+      <c r="P2" s="141" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:20" s="5" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="144"/>
-      <c r="B3" s="145"/>
+    <row r="3" spans="1:16" s="5" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="143"/>
+      <c r="B3" s="141"/>
       <c r="C3" s="72" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="87" t="s">
+      <c r="D3" s="86" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="71" t="s">
@@ -3193,16 +2925,12 @@
       <c r="L3" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="145"/>
-      <c r="N3" s="145"/>
-      <c r="O3" s="146"/>
-      <c r="P3" s="145"/>
-      <c r="Q3" s="145"/>
-      <c r="R3" s="145"/>
-      <c r="S3" s="145"/>
-      <c r="T3" s="145"/>
-    </row>
-    <row r="4" spans="1:20" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M3" s="141"/>
+      <c r="N3" s="141"/>
+      <c r="O3" s="144"/>
+      <c r="P3" s="141"/>
+    </row>
+    <row r="4" spans="1:16" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="71" t="s">
         <v>1</v>
       </c>
@@ -3248,23 +2976,11 @@
       <c r="O4" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="P4" s="71" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q4" s="71" t="s">
-        <v>55</v>
-      </c>
-      <c r="R4" s="71" t="s">
-        <v>56</v>
-      </c>
-      <c r="S4" s="71" t="s">
-        <v>57</v>
-      </c>
-      <c r="T4" s="92" t="s">
+      <c r="P4" s="91" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:20" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="73">
         <v>1</v>
       </c>
@@ -3312,25 +3028,9 @@
         <f t="shared" ref="O5:O19" si="1">D5-M5</f>
         <v>0</v>
       </c>
-      <c r="P5" s="76">
-        <f t="shared" ref="P5:P19" si="2">IF(D5=0,"-",(M5/D5))</f>
-        <v>1</v>
-      </c>
-      <c r="Q5" s="76">
-        <f t="shared" ref="Q5:Q12" si="3">IF(D5=0,"-",(N5/D5))</f>
-        <v>0</v>
-      </c>
-      <c r="R5" s="76">
-        <f t="shared" ref="R5:R19" si="4">IF(D5=0,"-",(O5/D5))</f>
-        <v>0</v>
-      </c>
-      <c r="S5" s="76">
-        <f t="shared" ref="S5:S19" si="5">IF(D5=0,"-",(Q5+R5))</f>
-        <v>0</v>
-      </c>
-      <c r="T5" s="92"/>
-    </row>
-    <row r="6" spans="1:20" s="12" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="P5" s="91"/>
+    </row>
+    <row r="6" spans="1:16" s="12" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="73">
         <v>2</v>
       </c>
@@ -3378,27 +3078,11 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="P6" s="76">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q6" s="76">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R6" s="76">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S6" s="76">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="T6" s="116" t="s">
+      <c r="P6" s="115" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="7" spans="1:20" s="120" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" s="119" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="73">
         <v>3</v>
       </c>
@@ -3435,7 +3119,7 @@
       <c r="L7" s="75">
         <v>0</v>
       </c>
-      <c r="M7" s="119">
+      <c r="M7" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3446,31 +3130,15 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="P7" s="76">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q7" s="76">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R7" s="76">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S7" s="76">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="T7" s="116" t="s">
+      <c r="P7" s="115" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="8" spans="1:20" s="120" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" s="119" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="73">
         <v>4</v>
       </c>
-      <c r="B8" s="117" t="s">
+      <c r="B8" s="116" t="s">
         <v>191</v>
       </c>
       <c r="C8" s="73">
@@ -3503,7 +3171,7 @@
       <c r="L8" s="73">
         <v>0</v>
       </c>
-      <c r="M8" s="119">
+      <c r="M8" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3514,27 +3182,11 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="P8" s="76">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="76">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R8" s="76">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S8" s="76">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="T8" s="116" t="s">
+      <c r="P8" s="115" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="9" spans="1:20" s="120" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" s="119" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="73">
         <v>5</v>
       </c>
@@ -3571,7 +3223,7 @@
       <c r="L9" s="73">
         <v>0</v>
       </c>
-      <c r="M9" s="119">
+      <c r="M9" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3582,91 +3234,59 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="P9" s="76">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="76">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R9" s="76">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S9" s="76">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="T9" s="116"/>
-    </row>
-    <row r="10" spans="1:20" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="132">
+      <c r="P9" s="115"/>
+    </row>
+    <row r="10" spans="1:16" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="131">
         <v>6</v>
       </c>
-      <c r="B10" s="133" t="s">
+      <c r="B10" s="132" t="s">
         <v>185</v>
       </c>
-      <c r="C10" s="132">
+      <c r="C10" s="131">
         <v>5</v>
       </c>
-      <c r="D10" s="132">
-        <v>1</v>
-      </c>
-      <c r="E10" s="132">
-        <v>0</v>
-      </c>
-      <c r="F10" s="132">
-        <v>0</v>
-      </c>
-      <c r="G10" s="132">
-        <v>0</v>
-      </c>
-      <c r="H10" s="132">
-        <v>0</v>
-      </c>
-      <c r="I10" s="132">
-        <v>0</v>
-      </c>
-      <c r="J10" s="132">
-        <v>0</v>
-      </c>
-      <c r="K10" s="132">
-        <v>0</v>
-      </c>
-      <c r="L10" s="132">
-        <v>0</v>
-      </c>
-      <c r="M10" s="119">
+      <c r="D10" s="131">
+        <v>1</v>
+      </c>
+      <c r="E10" s="131">
+        <v>0</v>
+      </c>
+      <c r="F10" s="131">
+        <v>0</v>
+      </c>
+      <c r="G10" s="131">
+        <v>0</v>
+      </c>
+      <c r="H10" s="131">
+        <v>0</v>
+      </c>
+      <c r="I10" s="131">
+        <v>0</v>
+      </c>
+      <c r="J10" s="131">
+        <v>0</v>
+      </c>
+      <c r="K10" s="131">
+        <v>0</v>
+      </c>
+      <c r="L10" s="131">
+        <v>0</v>
+      </c>
+      <c r="M10" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N10" s="134">
-        <v>0</v>
-      </c>
-      <c r="O10" s="134">
+      <c r="N10" s="133">
+        <v>0</v>
+      </c>
+      <c r="O10" s="133">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="P10" s="135">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q10" s="135">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R10" s="135">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S10" s="135">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="T10" s="136"/>
-    </row>
-    <row r="11" spans="1:20" s="120" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="P10" s="134"/>
+    </row>
+    <row r="11" spans="1:16" s="119" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="73">
         <v>7</v>
       </c>
@@ -3703,7 +3323,7 @@
       <c r="L11" s="75">
         <v>0</v>
       </c>
-      <c r="M11" s="119">
+      <c r="M11" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3714,25 +3334,9 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="P11" s="76">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="76">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R11" s="76">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S11" s="76">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="T11" s="116"/>
-    </row>
-    <row r="12" spans="1:20" s="56" customFormat="1" ht="30" x14ac:dyDescent="0.3">
+      <c r="P11" s="115"/>
+    </row>
+    <row r="12" spans="1:16" s="56" customFormat="1" ht="30" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>8</v>
       </c>
@@ -3769,7 +3373,7 @@
       <c r="L12" s="7">
         <v>0</v>
       </c>
-      <c r="M12" s="82">
+      <c r="M12" s="81">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -3780,31 +3384,15 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="P12" s="8">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="Q12" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R12" s="8">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-      <c r="S12" s="8">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
-      </c>
-      <c r="T12" s="138" t="s">
+      <c r="P12" s="136" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="13" spans="1:20" s="12" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" s="12" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="73">
         <v>9</v>
       </c>
-      <c r="B13" s="117" t="s">
+      <c r="B13" s="116" t="s">
         <v>197</v>
       </c>
       <c r="C13" s="75">
@@ -3848,30 +3436,15 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="P13" s="76">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="76">
-        <v>0</v>
-      </c>
-      <c r="R13" s="76">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S13" s="76">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="T13" s="118" t="s">
+      <c r="P13" s="117" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="14" spans="1:20" s="12" customFormat="1" ht="75" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" s="12" customFormat="1" ht="75" x14ac:dyDescent="0.3">
       <c r="A14" s="73">
         <v>10</v>
       </c>
-      <c r="B14" s="77" t="s">
+      <c r="B14" s="76" t="s">
         <v>195</v>
       </c>
       <c r="C14" s="73">
@@ -3915,27 +3488,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="P14" s="76">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="Q14" s="76">
-        <f t="shared" ref="Q14:Q19" si="6">IF(D14=0,"-",(N14/D14))</f>
-        <v>0</v>
-      </c>
-      <c r="R14" s="76">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-      <c r="S14" s="76">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
-      </c>
-      <c r="T14" s="93" t="s">
+      <c r="P14" s="92" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="15" spans="1:20" s="12" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" s="12" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="73">
         <v>11</v>
       </c>
@@ -3983,29 +3540,13 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="P15" s="76">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="76">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R15" s="76">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S15" s="76">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="T15" s="116"/>
-    </row>
-    <row r="16" spans="1:20" s="120" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P15" s="115"/>
+    </row>
+    <row r="16" spans="1:16" s="119" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="73">
         <v>12</v>
       </c>
-      <c r="B16" s="117" t="s">
+      <c r="B16" s="116" t="s">
         <v>192</v>
       </c>
       <c r="C16" s="73">
@@ -4038,7 +3579,7 @@
       <c r="L16" s="73">
         <v>0</v>
       </c>
-      <c r="M16" s="119">
+      <c r="M16" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4049,27 +3590,11 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="P16" s="76">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="76">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="76">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S16" s="76">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="T16" s="116" t="s">
+      <c r="P16" s="115" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="17" spans="1:20" s="120" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" s="119" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="73">
         <v>13</v>
       </c>
@@ -4106,7 +3631,7 @@
       <c r="L17" s="75">
         <v>0</v>
       </c>
-      <c r="M17" s="119">
+      <c r="M17" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4117,27 +3642,11 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="P17" s="76">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="76">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R17" s="76">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S17" s="76">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="T17" s="116" t="s">
+      <c r="P17" s="115" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="18" spans="1:20" s="120" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" s="119" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="73">
         <v>14</v>
       </c>
@@ -4174,7 +3683,7 @@
       <c r="L18" s="75">
         <v>0</v>
       </c>
-      <c r="M18" s="119">
+      <c r="M18" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4185,29 +3694,13 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="P18" s="76">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="76">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R18" s="76">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S18" s="76">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="T18" s="116"/>
-    </row>
-    <row r="19" spans="1:20" s="120" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P18" s="115"/>
+    </row>
+    <row r="19" spans="1:16" s="119" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="73">
         <v>15</v>
       </c>
-      <c r="B19" s="117" t="s">
+      <c r="B19" s="116" t="s">
         <v>194</v>
       </c>
       <c r="C19" s="73">
@@ -4240,7 +3733,7 @@
       <c r="L19" s="73">
         <v>0</v>
       </c>
-      <c r="M19" s="119">
+      <c r="M19" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4251,41 +3744,21 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="P19" s="76">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="76">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R19" s="76">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S19" s="76">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="T19" s="116" t="s">
+      <c r="P19" s="115" t="s">
         <v>155</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="E2:L2"/>
-    <mergeCell ref="A1:T1"/>
+  <mergeCells count="9">
+    <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:D2"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="P2:P3"/>
     <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="E2:L2"/>
   </mergeCells>
   <conditionalFormatting sqref="B8">
     <cfRule type="duplicateValues" dxfId="9" priority="7" stopIfTrue="1"/>
@@ -4351,187 +3824,187 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="R1" s="151" t="s">
+      <c r="R1" s="145" t="s">
         <v>163</v>
       </c>
-      <c r="S1" s="151"/>
-      <c r="T1" s="151"/>
+      <c r="S1" s="145"/>
+      <c r="T1" s="145"/>
     </row>
     <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="143" t="s">
+      <c r="A2" s="142" t="s">
         <v>150</v>
       </c>
-      <c r="B2" s="143"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="143"/>
-      <c r="K2" s="143"/>
-      <c r="L2" s="143"/>
-      <c r="M2" s="143"/>
-      <c r="N2" s="143"/>
-      <c r="O2" s="143"/>
-      <c r="P2" s="143"/>
-      <c r="Q2" s="143"/>
-      <c r="R2" s="143"/>
-      <c r="S2" s="143"/>
-      <c r="T2" s="143"/>
+      <c r="B2" s="142"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="142"/>
+      <c r="G2" s="142"/>
+      <c r="H2" s="142"/>
+      <c r="I2" s="142"/>
+      <c r="J2" s="142"/>
+      <c r="K2" s="142"/>
+      <c r="L2" s="142"/>
+      <c r="M2" s="142"/>
+      <c r="N2" s="142"/>
+      <c r="O2" s="142"/>
+      <c r="P2" s="142"/>
+      <c r="Q2" s="142"/>
+      <c r="R2" s="142"/>
+      <c r="S2" s="142"/>
+      <c r="T2" s="142"/>
     </row>
     <row r="3" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="R3" s="148"/>
       <c r="S3" s="149"/>
     </row>
     <row r="4" spans="1:20" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="146" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="150" t="s">
+      <c r="A4" s="144" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="146" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="146" t="s">
+      <c r="C4" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146" t="s">
+      <c r="D4" s="144"/>
+      <c r="E4" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="146"/>
-      <c r="K4" s="146"/>
-      <c r="L4" s="146"/>
-      <c r="M4" s="150" t="s">
+      <c r="F4" s="144"/>
+      <c r="G4" s="144"/>
+      <c r="H4" s="144"/>
+      <c r="I4" s="144"/>
+      <c r="J4" s="144"/>
+      <c r="K4" s="144"/>
+      <c r="L4" s="144"/>
+      <c r="M4" s="146" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="150" t="s">
+      <c r="N4" s="146" t="s">
         <v>20</v>
       </c>
-      <c r="O4" s="146" t="s">
+      <c r="O4" s="144" t="s">
         <v>47</v>
       </c>
-      <c r="P4" s="150" t="s">
+      <c r="P4" s="146" t="s">
         <v>22</v>
       </c>
-      <c r="Q4" s="150" t="s">
+      <c r="Q4" s="146" t="s">
         <v>23</v>
       </c>
-      <c r="R4" s="150" t="s">
+      <c r="R4" s="146" t="s">
         <v>24</v>
       </c>
-      <c r="S4" s="150" t="s">
+      <c r="S4" s="146" t="s">
         <v>25</v>
       </c>
-      <c r="T4" s="146" t="s">
+      <c r="T4" s="144" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:20" s="16" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="146"/>
-      <c r="B5" s="150"/>
-      <c r="C5" s="87" t="s">
+      <c r="A5" s="144"/>
+      <c r="B5" s="146"/>
+      <c r="C5" s="86" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="87" t="s">
+      <c r="D5" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="98" t="s">
+      <c r="E5" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="98" t="s">
+      <c r="F5" s="97" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="98" t="s">
+      <c r="G5" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="98" t="s">
+      <c r="H5" s="97" t="s">
         <v>50</v>
       </c>
-      <c r="I5" s="98" t="s">
+      <c r="I5" s="97" t="s">
         <v>51</v>
       </c>
-      <c r="J5" s="98" t="s">
+      <c r="J5" s="97" t="s">
         <v>52</v>
       </c>
-      <c r="K5" s="98" t="s">
+      <c r="K5" s="97" t="s">
         <v>53</v>
       </c>
-      <c r="L5" s="98" t="s">
+      <c r="L5" s="97" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="150"/>
-      <c r="N5" s="150"/>
-      <c r="O5" s="146"/>
-      <c r="P5" s="150"/>
-      <c r="Q5" s="150"/>
-      <c r="R5" s="150"/>
-      <c r="S5" s="150"/>
-      <c r="T5" s="146"/>
+      <c r="M5" s="146"/>
+      <c r="N5" s="146"/>
+      <c r="O5" s="144"/>
+      <c r="P5" s="146"/>
+      <c r="Q5" s="146"/>
+      <c r="R5" s="146"/>
+      <c r="S5" s="146"/>
+      <c r="T5" s="144"/>
     </row>
     <row r="6" spans="1:20" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="98" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="87" t="s">
+      <c r="A6" s="97" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="98" t="s">
+      <c r="C6" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="98" t="s">
+      <c r="D6" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="98" t="s">
+      <c r="E6" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="98" t="s">
+      <c r="F6" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="98" t="s">
+      <c r="G6" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="98" t="s">
+      <c r="H6" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="98" t="s">
+      <c r="I6" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="J6" s="98" t="s">
+      <c r="J6" s="97" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="98" t="s">
+      <c r="K6" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="L6" s="98" t="s">
+      <c r="L6" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="M6" s="98" t="s">
+      <c r="M6" s="97" t="s">
         <v>13</v>
       </c>
-      <c r="N6" s="98" t="s">
+      <c r="N6" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="O6" s="98" t="s">
+      <c r="O6" s="97" t="s">
         <v>32</v>
       </c>
-      <c r="P6" s="98" t="s">
+      <c r="P6" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="Q6" s="98" t="s">
+      <c r="Q6" s="97" t="s">
         <v>55</v>
       </c>
-      <c r="R6" s="98" t="s">
+      <c r="R6" s="97" t="s">
         <v>56</v>
       </c>
-      <c r="S6" s="98" t="s">
+      <c r="S6" s="97" t="s">
         <v>57</v>
       </c>
-      <c r="T6" s="98" t="s">
+      <c r="T6" s="97" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4540,24 +4013,24 @@
         <v>62</v>
       </c>
       <c r="B7" s="147"/>
-      <c r="C7" s="98"/>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="98"/>
-      <c r="J7" s="98"/>
-      <c r="K7" s="98"/>
-      <c r="L7" s="98"/>
-      <c r="M7" s="98"/>
-      <c r="N7" s="98"/>
-      <c r="O7" s="98"/>
-      <c r="P7" s="98"/>
-      <c r="Q7" s="98"/>
-      <c r="R7" s="98"/>
-      <c r="S7" s="98"/>
-      <c r="T7" s="98"/>
+      <c r="C7" s="97"/>
+      <c r="D7" s="97"/>
+      <c r="E7" s="97"/>
+      <c r="F7" s="97"/>
+      <c r="G7" s="97"/>
+      <c r="H7" s="97"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="97"/>
+      <c r="L7" s="97"/>
+      <c r="M7" s="97"/>
+      <c r="N7" s="97"/>
+      <c r="O7" s="97"/>
+      <c r="P7" s="97"/>
+      <c r="Q7" s="97"/>
+      <c r="R7" s="97"/>
+      <c r="S7" s="97"/>
+      <c r="T7" s="97"/>
     </row>
     <row r="8" spans="1:20" s="58" customFormat="1" ht="30" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
@@ -4590,22 +4063,22 @@
       <c r="J8" s="25">
         <v>0</v>
       </c>
-      <c r="K8" s="85">
-        <v>0</v>
-      </c>
-      <c r="L8" s="85">
+      <c r="K8" s="84">
+        <v>0</v>
+      </c>
+      <c r="L8" s="84">
         <v>0</v>
       </c>
       <c r="M8" s="30">
         <v>0</v>
       </c>
-      <c r="N8" s="85">
-        <v>0</v>
-      </c>
-      <c r="O8" s="111">
+      <c r="N8" s="84">
+        <v>0</v>
+      </c>
+      <c r="O8" s="110">
         <v>32</v>
       </c>
-      <c r="P8" s="86">
+      <c r="P8" s="85">
         <f>IF(D8=0,"-",(M8/D8))</f>
         <v>0</v>
       </c>
@@ -4621,12 +4094,20 @@
         <f>IF(D8=0,"-",(Q8+R8))</f>
         <v>1</v>
       </c>
-      <c r="T8" s="137" t="s">
+      <c r="T8" s="135" t="s">
         <v>168</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:L4"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
     <mergeCell ref="A2:T2"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="R1:T1"/>
@@ -4635,14 +4116,6 @@
     <mergeCell ref="Q4:Q5"/>
     <mergeCell ref="R4:R5"/>
     <mergeCell ref="S4:S5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:L4"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:N5"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C8:L8" xr:uid="{E60E427C-1D50-4378-A1E0-5F50F54ADE56}">
@@ -4695,33 +4168,33 @@
       <c r="I1" s="4"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-      <c r="N1" s="153" t="s">
+      <c r="N1" s="151" t="s">
         <v>162</v>
       </c>
-      <c r="O1" s="153"/>
-      <c r="P1" s="153"/>
-      <c r="Q1" s="153"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
     </row>
     <row r="2" spans="1:92" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="154" t="s">
+      <c r="A2" s="152" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="154"/>
-      <c r="C2" s="154"/>
-      <c r="D2" s="154"/>
-      <c r="E2" s="154"/>
-      <c r="F2" s="154"/>
-      <c r="G2" s="154"/>
-      <c r="H2" s="154"/>
-      <c r="I2" s="154"/>
-      <c r="J2" s="154"/>
-      <c r="K2" s="154"/>
-      <c r="L2" s="154"/>
-      <c r="M2" s="154"/>
-      <c r="N2" s="154"/>
-      <c r="O2" s="154"/>
-      <c r="P2" s="154"/>
-      <c r="Q2" s="154"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="152"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="152"/>
+      <c r="F2" s="152"/>
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="152"/>
+      <c r="K2" s="152"/>
+      <c r="L2" s="152"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="152"/>
+      <c r="O2" s="152"/>
+      <c r="P2" s="152"/>
+      <c r="Q2" s="152"/>
     </row>
     <row r="3" spans="1:92" s="13" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -4743,55 +4216,55 @@
       <c r="Q3" s="149"/>
     </row>
     <row r="4" spans="1:92" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="146" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="150" t="s">
+      <c r="A4" s="144" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="146" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="146" t="s">
+      <c r="C4" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146" t="s">
+      <c r="D4" s="144"/>
+      <c r="E4" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="150" t="s">
+      <c r="F4" s="144"/>
+      <c r="G4" s="144"/>
+      <c r="H4" s="144"/>
+      <c r="I4" s="144"/>
+      <c r="J4" s="146" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="150" t="s">
+      <c r="K4" s="146" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="150" t="s">
+      <c r="L4" s="146" t="s">
         <v>21</v>
       </c>
-      <c r="M4" s="150" t="s">
+      <c r="M4" s="146" t="s">
         <v>22</v>
       </c>
-      <c r="N4" s="150" t="s">
+      <c r="N4" s="146" t="s">
         <v>23</v>
       </c>
-      <c r="O4" s="150" t="s">
+      <c r="O4" s="146" t="s">
         <v>24</v>
       </c>
-      <c r="P4" s="150" t="s">
+      <c r="P4" s="146" t="s">
         <v>25</v>
       </c>
-      <c r="Q4" s="150" t="s">
+      <c r="Q4" s="146" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:92" s="55" customFormat="1" ht="74.400000000000006" x14ac:dyDescent="0.3">
-      <c r="A5" s="146"/>
-      <c r="B5" s="150"/>
-      <c r="C5" s="95" t="s">
+      <c r="A5" s="144"/>
+      <c r="B5" s="146"/>
+      <c r="C5" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="95" t="s">
+      <c r="D5" s="94" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="53" t="s">
@@ -4809,62 +4282,62 @@
       <c r="I5" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="150"/>
-      <c r="K5" s="150"/>
-      <c r="L5" s="150"/>
-      <c r="M5" s="150"/>
-      <c r="N5" s="150"/>
-      <c r="O5" s="150"/>
-      <c r="P5" s="150"/>
-      <c r="Q5" s="146"/>
+      <c r="J5" s="146"/>
+      <c r="K5" s="146"/>
+      <c r="L5" s="146"/>
+      <c r="M5" s="146"/>
+      <c r="N5" s="146"/>
+      <c r="O5" s="146"/>
+      <c r="P5" s="146"/>
+      <c r="Q5" s="144"/>
     </row>
     <row r="6" spans="1:92" s="17" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="88" t="s">
+      <c r="A6" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="89" t="s">
+      <c r="C6" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="89" t="s">
+      <c r="D6" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="89" t="s">
+      <c r="E6" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="89" t="s">
+      <c r="F6" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="89" t="s">
+      <c r="G6" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="89" t="s">
+      <c r="H6" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="89" t="s">
+      <c r="I6" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="J6" s="89" t="s">
+      <c r="J6" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="89" t="s">
+      <c r="K6" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="L6" s="89" t="s">
+      <c r="L6" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="M6" s="89" t="s">
+      <c r="M6" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="N6" s="89" t="s">
+      <c r="N6" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="O6" s="89" t="s">
+      <c r="O6" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="P6" s="89" t="s">
+      <c r="P6" s="88" t="s">
         <v>54</v>
       </c>
       <c r="Q6" s="32" t="s">
@@ -4872,87 +4345,87 @@
       </c>
     </row>
     <row r="7" spans="1:92" s="18" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="152" t="s">
+      <c r="A7" s="150" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="152"/>
-      <c r="C7" s="152"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="152"/>
-      <c r="F7" s="152"/>
-      <c r="G7" s="152"/>
-      <c r="H7" s="152"/>
-      <c r="I7" s="152"/>
-      <c r="J7" s="152"/>
-      <c r="K7" s="152"/>
-      <c r="L7" s="152"/>
-      <c r="M7" s="152"/>
-      <c r="N7" s="152"/>
-      <c r="O7" s="152"/>
-      <c r="P7" s="152"/>
-      <c r="Q7" s="152"/>
+      <c r="B7" s="150"/>
+      <c r="C7" s="150"/>
+      <c r="D7" s="150"/>
+      <c r="E7" s="150"/>
+      <c r="F7" s="150"/>
+      <c r="G7" s="150"/>
+      <c r="H7" s="150"/>
+      <c r="I7" s="150"/>
+      <c r="J7" s="150"/>
+      <c r="K7" s="150"/>
+      <c r="L7" s="150"/>
+      <c r="M7" s="150"/>
+      <c r="N7" s="150"/>
+      <c r="O7" s="150"/>
+      <c r="P7" s="150"/>
+      <c r="Q7" s="150"/>
     </row>
     <row r="8" spans="1:92" s="19" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="99">
-        <v>1</v>
-      </c>
-      <c r="B8" s="100" t="s">
+      <c r="A8" s="98">
+        <v>1</v>
+      </c>
+      <c r="B8" s="99" t="s">
         <v>200</v>
       </c>
-      <c r="C8" s="101">
+      <c r="C8" s="100">
         <v>51</v>
       </c>
-      <c r="D8" s="101">
+      <c r="D8" s="100">
         <v>48</v>
       </c>
-      <c r="E8" s="101">
-        <v>0</v>
-      </c>
-      <c r="F8" s="101">
-        <v>0</v>
-      </c>
-      <c r="G8" s="101">
-        <v>0</v>
-      </c>
-      <c r="H8" s="101">
-        <v>0</v>
-      </c>
-      <c r="I8" s="101">
-        <v>0</v>
-      </c>
-      <c r="J8" s="99">
-        <v>0</v>
-      </c>
-      <c r="K8" s="101">
-        <v>0</v>
-      </c>
-      <c r="L8" s="102">
+      <c r="E8" s="100">
+        <v>0</v>
+      </c>
+      <c r="F8" s="100">
+        <v>0</v>
+      </c>
+      <c r="G8" s="100">
+        <v>0</v>
+      </c>
+      <c r="H8" s="100">
+        <v>0</v>
+      </c>
+      <c r="I8" s="100">
+        <v>0</v>
+      </c>
+      <c r="J8" s="98">
+        <v>0</v>
+      </c>
+      <c r="K8" s="100">
+        <v>0</v>
+      </c>
+      <c r="L8" s="101">
         <f>IF(D8=0,"-",D8-(J8+K8))</f>
         <v>48</v>
       </c>
-      <c r="M8" s="103">
+      <c r="M8" s="102">
         <f>J8/D8*100</f>
         <v>0</v>
       </c>
-      <c r="N8" s="103">
+      <c r="N8" s="102">
         <f>IF(D8=0,"-",(K8/D8))</f>
         <v>0</v>
       </c>
-      <c r="O8" s="103">
+      <c r="O8" s="102">
         <f>IF(D8=0,"-",(L8/D8))</f>
         <v>1</v>
       </c>
-      <c r="P8" s="103">
+      <c r="P8" s="102">
         <f>IF(D8=0,"-",(N8+O8))</f>
         <v>1</v>
       </c>
-      <c r="Q8" s="104"/>
+      <c r="Q8" s="103"/>
     </row>
     <row r="9" spans="1:92" s="18" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="50">
         <v>2</v>
       </c>
-      <c r="B9" s="105" t="s">
+      <c r="B9" s="104" t="s">
         <v>201</v>
       </c>
       <c r="C9" s="70">
@@ -4976,17 +4449,17 @@
       <c r="I9" s="70">
         <v>0</v>
       </c>
-      <c r="J9" s="99">
+      <c r="J9" s="98">
         <v>1</v>
       </c>
       <c r="K9" s="70">
         <v>0</v>
       </c>
-      <c r="L9" s="102">
+      <c r="L9" s="101">
         <f>IF(D9=0,"-",D9-(J9+K9))</f>
         <v>375</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="102">
         <f>J9/D9*100</f>
         <v>0.26595744680851063</v>
       </c>
@@ -5002,15 +4475,15 @@
         <f>IF(D9=0,"-",(N9+O9))</f>
         <v>0.99734042553191493</v>
       </c>
-      <c r="Q9" s="139" t="s">
+      <c r="Q9" s="137" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:92" s="18" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="106">
+      <c r="A10" s="105">
         <v>3</v>
       </c>
-      <c r="B10" s="107" t="s">
+      <c r="B10" s="106" t="s">
         <v>202</v>
       </c>
       <c r="C10" s="70">
@@ -5034,17 +4507,17 @@
       <c r="I10" s="70">
         <v>0</v>
       </c>
-      <c r="J10" s="99">
+      <c r="J10" s="98">
         <v>0</v>
       </c>
       <c r="K10" s="70">
         <v>0</v>
       </c>
-      <c r="L10" s="102">
+      <c r="L10" s="101">
         <f>IF(D10=0,"-",D10-(J10+K10))</f>
         <v>281</v>
       </c>
-      <c r="M10" s="103">
+      <c r="M10" s="102">
         <v>3.3999999999999998E-3</v>
       </c>
       <c r="N10" s="52">
@@ -5059,13 +4532,13 @@
         <f>IF(D10=0,"-",(N10+O10))</f>
         <v>1</v>
       </c>
-      <c r="Q10" s="113"/>
+      <c r="Q10" s="112"/>
     </row>
     <row r="11" spans="1:92" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A11" s="99">
+      <c r="A11" s="98">
         <v>4</v>
       </c>
-      <c r="B11" s="105" t="s">
+      <c r="B11" s="104" t="s">
         <v>203</v>
       </c>
       <c r="C11" s="70">
@@ -5095,11 +4568,11 @@
       <c r="K11" s="70">
         <v>0</v>
       </c>
-      <c r="L11" s="102">
+      <c r="L11" s="101">
         <f>IF(D11=0,"-",D11-(J11+K11))</f>
         <v>52</v>
       </c>
-      <c r="M11" s="103">
+      <c r="M11" s="102">
         <f>J11/D11*100</f>
         <v>0</v>
       </c>
@@ -5115,13 +4588,13 @@
         <f>IF(D11=0,"-",(N11+O11))</f>
         <v>1</v>
       </c>
-      <c r="Q11" s="108"/>
+      <c r="Q11" s="107"/>
     </row>
     <row r="12" spans="1:92" s="18" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="50">
         <v>5</v>
       </c>
-      <c r="B12" s="105" t="s">
+      <c r="B12" s="104" t="s">
         <v>204</v>
       </c>
       <c r="C12" s="70">
@@ -5154,7 +4627,7 @@
       <c r="L12" s="51">
         <v>0</v>
       </c>
-      <c r="M12" s="103">
+      <c r="M12" s="102">
         <v>0</v>
       </c>
       <c r="N12" s="52">
@@ -5168,13 +4641,13 @@
         <f>IF(D12=0,"-",(N12+O12))</f>
         <v>-</v>
       </c>
-      <c r="Q12" s="113"/>
-    </row>
-    <row r="13" spans="1:92" s="96" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="106">
+      <c r="Q12" s="112"/>
+    </row>
+    <row r="13" spans="1:92" s="95" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="105">
         <v>6</v>
       </c>
-      <c r="B13" s="105" t="s">
+      <c r="B13" s="104" t="s">
         <v>205</v>
       </c>
       <c r="C13" s="70">
@@ -5220,7 +4693,7 @@
       <c r="P13" s="52">
         <v>1</v>
       </c>
-      <c r="Q13" s="108" t="s">
+      <c r="Q13" s="107" t="s">
         <v>158</v>
       </c>
       <c r="R13" s="18"/>
@@ -5359,160 +4832,160 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="158"/>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="157" t="s">
+      <c r="A1" s="173"/>
+      <c r="B1" s="173"/>
+      <c r="C1" s="173"/>
+      <c r="D1" s="173"/>
+      <c r="E1" s="173"/>
+      <c r="F1" s="173"/>
+      <c r="G1" s="173"/>
+      <c r="H1" s="173"/>
+      <c r="I1" s="173"/>
+      <c r="J1" s="173"/>
+      <c r="K1" s="173"/>
+      <c r="L1" s="173"/>
+      <c r="M1" s="172" t="s">
         <v>170</v>
       </c>
-      <c r="N1" s="157"/>
-      <c r="O1" s="157"/>
-      <c r="P1" s="157"/>
+      <c r="N1" s="172"/>
+      <c r="O1" s="172"/>
+      <c r="P1" s="172"/>
     </row>
     <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="172" t="s">
+      <c r="A2" s="163" t="s">
         <v>148</v>
       </c>
-      <c r="B2" s="172"/>
-      <c r="C2" s="172"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="172"/>
-      <c r="G2" s="172"/>
-      <c r="H2" s="172"/>
-      <c r="I2" s="172"/>
-      <c r="J2" s="172"/>
-      <c r="K2" s="172"/>
-      <c r="L2" s="172"/>
-      <c r="M2" s="172"/>
-      <c r="N2" s="172"/>
-      <c r="O2" s="172"/>
-      <c r="P2" s="172"/>
+      <c r="B2" s="163"/>
+      <c r="C2" s="163"/>
+      <c r="D2" s="163"/>
+      <c r="E2" s="163"/>
+      <c r="F2" s="163"/>
+      <c r="G2" s="163"/>
+      <c r="H2" s="163"/>
+      <c r="I2" s="163"/>
+      <c r="J2" s="163"/>
+      <c r="K2" s="163"/>
+      <c r="L2" s="163"/>
+      <c r="M2" s="163"/>
+      <c r="N2" s="163"/>
+      <c r="O2" s="163"/>
+      <c r="P2" s="163"/>
     </row>
     <row r="3" spans="1:16" s="20" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="171" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="170" t="s">
+      <c r="A3" s="162" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="161" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171" t="s">
+      <c r="C3" s="161"/>
+      <c r="D3" s="162" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="171"/>
-      <c r="F3" s="171" t="s">
+      <c r="E3" s="162"/>
+      <c r="F3" s="162" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="171"/>
-      <c r="H3" s="171"/>
-      <c r="I3" s="170" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="161" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="170" t="s">
+      <c r="J3" s="161" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="170" t="s">
+      <c r="K3" s="161" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="170" t="s">
+      <c r="L3" s="161" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="170" t="s">
+      <c r="M3" s="161" t="s">
         <v>23</v>
       </c>
-      <c r="N3" s="170" t="s">
+      <c r="N3" s="161" t="s">
         <v>24</v>
       </c>
-      <c r="O3" s="170" t="s">
+      <c r="O3" s="161" t="s">
         <v>25</v>
       </c>
-      <c r="P3" s="173" t="s">
+      <c r="P3" s="164" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:16" s="20" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="171"/>
-      <c r="B4" s="170"/>
-      <c r="C4" s="170"/>
-      <c r="D4" s="88" t="s">
+      <c r="A4" s="162"/>
+      <c r="B4" s="161"/>
+      <c r="C4" s="161"/>
+      <c r="D4" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="88" t="s">
+      <c r="E4" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="89" t="s">
+      <c r="F4" s="88" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="88" t="s">
+      <c r="G4" s="87" t="s">
         <v>140</v>
       </c>
       <c r="H4" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="170"/>
-      <c r="J4" s="170"/>
-      <c r="K4" s="170"/>
-      <c r="L4" s="170"/>
-      <c r="M4" s="170"/>
-      <c r="N4" s="170"/>
-      <c r="O4" s="170"/>
-      <c r="P4" s="174"/>
+      <c r="I4" s="161"/>
+      <c r="J4" s="161"/>
+      <c r="K4" s="161"/>
+      <c r="L4" s="161"/>
+      <c r="M4" s="161"/>
+      <c r="N4" s="161"/>
+      <c r="O4" s="161"/>
+      <c r="P4" s="165"/>
     </row>
     <row r="5" spans="1:16" s="20" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="170" t="s">
+      <c r="A5" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="161" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="170"/>
-      <c r="D5" s="89" t="s">
+      <c r="C5" s="161"/>
+      <c r="D5" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="89" t="s">
+      <c r="E5" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="89" t="s">
+      <c r="F5" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="89" t="s">
+      <c r="G5" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="89" t="s">
+      <c r="H5" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="89" t="s">
+      <c r="I5" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="89" t="s">
+      <c r="J5" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="89" t="s">
+      <c r="K5" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="89" t="s">
+      <c r="L5" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="89" t="s">
+      <c r="M5" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="89" t="s">
+      <c r="N5" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="O5" s="89" t="s">
+      <c r="O5" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="P5" s="89" t="s">
+      <c r="P5" s="88" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5520,23 +4993,23 @@
       <c r="A6" s="28">
         <v>1</v>
       </c>
-      <c r="B6" s="91" t="s">
+      <c r="B6" s="90" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="91"/>
-      <c r="D6" s="160"/>
-      <c r="E6" s="160"/>
-      <c r="F6" s="160"/>
-      <c r="G6" s="160"/>
-      <c r="H6" s="160"/>
-      <c r="I6" s="160"/>
-      <c r="J6" s="160"/>
-      <c r="K6" s="169"/>
-      <c r="L6" s="161"/>
-      <c r="M6" s="161"/>
-      <c r="N6" s="161"/>
-      <c r="O6" s="161"/>
-      <c r="P6" s="159"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="167"/>
+      <c r="E6" s="167"/>
+      <c r="F6" s="167"/>
+      <c r="G6" s="167"/>
+      <c r="H6" s="167"/>
+      <c r="I6" s="167"/>
+      <c r="J6" s="167"/>
+      <c r="K6" s="168"/>
+      <c r="L6" s="169"/>
+      <c r="M6" s="169"/>
+      <c r="N6" s="169"/>
+      <c r="O6" s="169"/>
+      <c r="P6" s="174"/>
     </row>
     <row r="7" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="28"/>
@@ -5551,21 +5024,21 @@
       <c r="F7" s="33"/>
       <c r="G7" s="33"/>
       <c r="H7" s="33"/>
-      <c r="I7" s="160"/>
-      <c r="J7" s="160"/>
-      <c r="K7" s="169"/>
-      <c r="L7" s="161"/>
-      <c r="M7" s="161"/>
-      <c r="N7" s="161"/>
-      <c r="O7" s="161"/>
-      <c r="P7" s="159"/>
+      <c r="I7" s="167"/>
+      <c r="J7" s="167"/>
+      <c r="K7" s="168"/>
+      <c r="L7" s="169"/>
+      <c r="M7" s="169"/>
+      <c r="N7" s="169"/>
+      <c r="O7" s="169"/>
+      <c r="P7" s="174"/>
     </row>
     <row r="8" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="28"/>
-      <c r="B8" s="155" t="s">
+      <c r="B8" s="160" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="155" t="s">
+      <c r="C8" s="160" t="s">
         <v>65</v>
       </c>
       <c r="D8" s="33"/>
@@ -5627,13 +5100,13 @@
       <c r="P10" s="47"/>
     </row>
     <row r="11" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="168">
+      <c r="A11" s="166">
         <v>2</v>
       </c>
-      <c r="B11" s="162" t="s">
+      <c r="B11" s="154" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="162"/>
+      <c r="C11" s="154"/>
       <c r="D11" s="33"/>
       <c r="E11" s="33"/>
       <c r="F11" s="33"/>
@@ -5649,7 +5122,7 @@
       <c r="P11" s="47"/>
     </row>
     <row r="12" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="168"/>
+      <c r="A12" s="166"/>
       <c r="B12" s="29" t="s">
         <v>1</v>
       </c>
@@ -5671,7 +5144,7 @@
       <c r="P12" s="47"/>
     </row>
     <row r="13" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="168"/>
+      <c r="A13" s="166"/>
       <c r="B13" s="29" t="s">
         <v>2</v>
       </c>
@@ -5693,7 +5166,7 @@
       <c r="P13" s="47"/>
     </row>
     <row r="14" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="168"/>
+      <c r="A14" s="166"/>
       <c r="B14" s="29" t="s">
         <v>3</v>
       </c>
@@ -5715,13 +5188,13 @@
       <c r="P14" s="47"/>
     </row>
     <row r="15" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="168">
+      <c r="A15" s="166">
         <v>3</v>
       </c>
-      <c r="B15" s="162" t="s">
+      <c r="B15" s="154" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="162"/>
+      <c r="C15" s="154"/>
       <c r="D15" s="33"/>
       <c r="E15" s="33"/>
       <c r="F15" s="33"/>
@@ -5737,7 +5210,7 @@
       <c r="P15" s="47"/>
     </row>
     <row r="16" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="168"/>
+      <c r="A16" s="166"/>
       <c r="B16" s="29" t="s">
         <v>1</v>
       </c>
@@ -5759,7 +5232,7 @@
       <c r="P16" s="47"/>
     </row>
     <row r="17" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="168"/>
+      <c r="A17" s="166"/>
       <c r="B17" s="29" t="s">
         <v>2</v>
       </c>
@@ -5781,7 +5254,7 @@
       <c r="P17" s="47"/>
     </row>
     <row r="18" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="168"/>
+      <c r="A18" s="166"/>
       <c r="B18" s="29" t="s">
         <v>3</v>
       </c>
@@ -5803,7 +5276,7 @@
       <c r="P18" s="47"/>
     </row>
     <row r="19" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="168"/>
+      <c r="A19" s="166"/>
       <c r="B19" s="29" t="s">
         <v>4</v>
       </c>
@@ -5825,7 +5298,7 @@
       <c r="P19" s="47"/>
     </row>
     <row r="20" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="168"/>
+      <c r="A20" s="166"/>
       <c r="B20" s="29" t="s">
         <v>4</v>
       </c>
@@ -5847,13 +5320,13 @@
       <c r="P20" s="47"/>
     </row>
     <row r="21" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="168">
+      <c r="A21" s="166">
         <v>4</v>
       </c>
-      <c r="B21" s="162" t="s">
+      <c r="B21" s="154" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="162"/>
+      <c r="C21" s="154"/>
       <c r="D21" s="33"/>
       <c r="E21" s="33"/>
       <c r="F21" s="33"/>
@@ -5869,7 +5342,7 @@
       <c r="P21" s="47"/>
     </row>
     <row r="22" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="168"/>
+      <c r="A22" s="166"/>
       <c r="B22" s="29" t="s">
         <v>1</v>
       </c>
@@ -5891,7 +5364,7 @@
       <c r="P22" s="47"/>
     </row>
     <row r="23" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="168"/>
+      <c r="A23" s="166"/>
       <c r="B23" s="29" t="s">
         <v>2</v>
       </c>
@@ -5913,7 +5386,7 @@
       <c r="P23" s="47"/>
     </row>
     <row r="24" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="168"/>
+      <c r="A24" s="166"/>
       <c r="B24" s="29" t="s">
         <v>3</v>
       </c>
@@ -5935,7 +5408,7 @@
       <c r="P24" s="47"/>
     </row>
     <row r="25" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="168"/>
+      <c r="A25" s="166"/>
       <c r="B25" s="29" t="s">
         <v>4</v>
       </c>
@@ -5957,13 +5430,13 @@
       <c r="P25" s="47"/>
     </row>
     <row r="26" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="168">
+      <c r="A26" s="166">
         <v>5</v>
       </c>
-      <c r="B26" s="162" t="s">
+      <c r="B26" s="154" t="s">
         <v>81</v>
       </c>
-      <c r="C26" s="162"/>
+      <c r="C26" s="154"/>
       <c r="D26" s="33"/>
       <c r="E26" s="33"/>
       <c r="F26" s="33"/>
@@ -5979,7 +5452,7 @@
       <c r="P26" s="47"/>
     </row>
     <row r="27" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="168"/>
+      <c r="A27" s="166"/>
       <c r="B27" s="29" t="s">
         <v>1</v>
       </c>
@@ -6001,7 +5474,7 @@
       <c r="P27" s="47"/>
     </row>
     <row r="28" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="168"/>
+      <c r="A28" s="166"/>
       <c r="B28" s="29" t="s">
         <v>2</v>
       </c>
@@ -6023,13 +5496,13 @@
       <c r="P28" s="47"/>
     </row>
     <row r="29" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="168">
+      <c r="A29" s="166">
         <v>6</v>
       </c>
-      <c r="B29" s="162" t="s">
+      <c r="B29" s="154" t="s">
         <v>83</v>
       </c>
-      <c r="C29" s="162"/>
+      <c r="C29" s="154"/>
       <c r="D29" s="33"/>
       <c r="E29" s="33"/>
       <c r="F29" s="33"/>
@@ -6045,7 +5518,7 @@
       <c r="P29" s="47"/>
     </row>
     <row r="30" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="168"/>
+      <c r="A30" s="166"/>
       <c r="B30" s="29" t="s">
         <v>1</v>
       </c>
@@ -6067,7 +5540,7 @@
       <c r="P30" s="47"/>
     </row>
     <row r="31" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="168"/>
+      <c r="A31" s="166"/>
       <c r="B31" s="29" t="s">
         <v>2</v>
       </c>
@@ -6089,7 +5562,7 @@
       <c r="P31" s="47"/>
     </row>
     <row r="32" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="168"/>
+      <c r="A32" s="166"/>
       <c r="B32" s="29" t="s">
         <v>3</v>
       </c>
@@ -6111,7 +5584,7 @@
       <c r="P32" s="47"/>
     </row>
     <row r="33" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="168"/>
+      <c r="A33" s="166"/>
       <c r="B33" s="29" t="s">
         <v>4</v>
       </c>
@@ -6133,7 +5606,7 @@
       <c r="P33" s="47"/>
     </row>
     <row r="34" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="168"/>
+      <c r="A34" s="166"/>
       <c r="B34" s="29" t="s">
         <v>5</v>
       </c>
@@ -6155,13 +5628,13 @@
       <c r="P34" s="47"/>
     </row>
     <row r="35" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="168">
+      <c r="A35" s="166">
         <v>7</v>
       </c>
-      <c r="B35" s="162" t="s">
+      <c r="B35" s="154" t="s">
         <v>88</v>
       </c>
-      <c r="C35" s="162"/>
+      <c r="C35" s="154"/>
       <c r="D35" s="33"/>
       <c r="E35" s="33"/>
       <c r="F35" s="33"/>
@@ -6177,7 +5650,7 @@
       <c r="P35" s="47"/>
     </row>
     <row r="36" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="168"/>
+      <c r="A36" s="166"/>
       <c r="B36" s="29" t="s">
         <v>1</v>
       </c>
@@ -6199,7 +5672,7 @@
       <c r="P36" s="47"/>
     </row>
     <row r="37" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="168"/>
+      <c r="A37" s="166"/>
       <c r="B37" s="29" t="s">
         <v>2</v>
       </c>
@@ -6221,7 +5694,7 @@
       <c r="P37" s="47"/>
     </row>
     <row r="38" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="168"/>
+      <c r="A38" s="166"/>
       <c r="B38" s="29" t="s">
         <v>3</v>
       </c>
@@ -6243,7 +5716,7 @@
       <c r="P38" s="47"/>
     </row>
     <row r="39" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="168"/>
+      <c r="A39" s="166"/>
       <c r="B39" s="29" t="s">
         <v>4</v>
       </c>
@@ -6265,13 +5738,13 @@
       <c r="P39" s="47"/>
     </row>
     <row r="40" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="168">
+      <c r="A40" s="166">
         <v>8</v>
       </c>
-      <c r="B40" s="162" t="s">
+      <c r="B40" s="154" t="s">
         <v>92</v>
       </c>
-      <c r="C40" s="162"/>
+      <c r="C40" s="154"/>
       <c r="D40" s="33"/>
       <c r="E40" s="33"/>
       <c r="F40" s="33"/>
@@ -6287,7 +5760,7 @@
       <c r="P40" s="47"/>
     </row>
     <row r="41" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="168"/>
+      <c r="A41" s="166"/>
       <c r="B41" s="29" t="s">
         <v>1</v>
       </c>
@@ -6309,7 +5782,7 @@
       <c r="P41" s="47"/>
     </row>
     <row r="42" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="168"/>
+      <c r="A42" s="166"/>
       <c r="B42" s="29" t="s">
         <v>2</v>
       </c>
@@ -6331,13 +5804,13 @@
       <c r="P42" s="47"/>
     </row>
     <row r="43" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="168">
+      <c r="A43" s="166">
         <v>9</v>
       </c>
-      <c r="B43" s="162" t="s">
+      <c r="B43" s="154" t="s">
         <v>95</v>
       </c>
-      <c r="C43" s="162"/>
+      <c r="C43" s="154"/>
       <c r="D43" s="33"/>
       <c r="E43" s="33"/>
       <c r="F43" s="33"/>
@@ -6353,7 +5826,7 @@
       <c r="P43" s="47"/>
     </row>
     <row r="44" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="168"/>
+      <c r="A44" s="166"/>
       <c r="B44" s="29" t="s">
         <v>1</v>
       </c>
@@ -6375,7 +5848,7 @@
       <c r="P44" s="47"/>
     </row>
     <row r="45" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="168"/>
+      <c r="A45" s="166"/>
       <c r="B45" s="29" t="s">
         <v>2</v>
       </c>
@@ -6397,7 +5870,7 @@
       <c r="P45" s="47"/>
     </row>
     <row r="46" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="168"/>
+      <c r="A46" s="166"/>
       <c r="B46" s="29" t="s">
         <v>3</v>
       </c>
@@ -6419,7 +5892,7 @@
       <c r="P46" s="47"/>
     </row>
     <row r="47" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="168"/>
+      <c r="A47" s="166"/>
       <c r="B47" s="29" t="s">
         <v>4</v>
       </c>
@@ -6441,13 +5914,13 @@
       <c r="P47" s="47"/>
     </row>
     <row r="48" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="168">
+      <c r="A48" s="166">
         <v>10</v>
       </c>
-      <c r="B48" s="162" t="s">
+      <c r="B48" s="154" t="s">
         <v>100</v>
       </c>
-      <c r="C48" s="162"/>
+      <c r="C48" s="154"/>
       <c r="D48" s="33"/>
       <c r="E48" s="33"/>
       <c r="F48" s="33"/>
@@ -6463,7 +5936,7 @@
       <c r="P48" s="47"/>
     </row>
     <row r="49" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="168"/>
+      <c r="A49" s="166"/>
       <c r="B49" s="29" t="s">
         <v>1</v>
       </c>
@@ -6485,7 +5958,7 @@
       <c r="P49" s="47"/>
     </row>
     <row r="50" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="168"/>
+      <c r="A50" s="166"/>
       <c r="B50" s="29" t="s">
         <v>2</v>
       </c>
@@ -6507,7 +5980,7 @@
       <c r="P50" s="47"/>
     </row>
     <row r="51" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="168"/>
+      <c r="A51" s="166"/>
       <c r="B51" s="29" t="s">
         <v>3</v>
       </c>
@@ -6529,7 +6002,7 @@
       <c r="P51" s="47"/>
     </row>
     <row r="52" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="168"/>
+      <c r="A52" s="166"/>
       <c r="B52" s="29" t="s">
         <v>4</v>
       </c>
@@ -6551,13 +6024,13 @@
       <c r="P52" s="47"/>
     </row>
     <row r="53" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="168">
+      <c r="A53" s="166">
         <v>11</v>
       </c>
-      <c r="B53" s="162" t="s">
+      <c r="B53" s="154" t="s">
         <v>104</v>
       </c>
-      <c r="C53" s="162"/>
+      <c r="C53" s="154"/>
       <c r="D53" s="33"/>
       <c r="E53" s="33"/>
       <c r="F53" s="33"/>
@@ -6573,7 +6046,7 @@
       <c r="P53" s="47"/>
     </row>
     <row r="54" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="168"/>
+      <c r="A54" s="166"/>
       <c r="B54" s="29" t="s">
         <v>1</v>
       </c>
@@ -6595,7 +6068,7 @@
       <c r="P54" s="47"/>
     </row>
     <row r="55" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="168"/>
+      <c r="A55" s="166"/>
       <c r="B55" s="29" t="s">
         <v>2</v>
       </c>
@@ -6617,13 +6090,13 @@
       <c r="P55" s="47"/>
     </row>
     <row r="56" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="168">
+      <c r="A56" s="166">
         <v>12</v>
       </c>
-      <c r="B56" s="162" t="s">
+      <c r="B56" s="154" t="s">
         <v>106</v>
       </c>
-      <c r="C56" s="162"/>
+      <c r="C56" s="154"/>
       <c r="D56" s="33"/>
       <c r="E56" s="33"/>
       <c r="F56" s="33"/>
@@ -6639,7 +6112,7 @@
       <c r="P56" s="47"/>
     </row>
     <row r="57" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="168"/>
+      <c r="A57" s="166"/>
       <c r="B57" s="29" t="s">
         <v>1</v>
       </c>
@@ -6661,13 +6134,13 @@
       <c r="P57" s="47"/>
     </row>
     <row r="58" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="168">
+      <c r="A58" s="166">
         <v>13</v>
       </c>
-      <c r="B58" s="162" t="s">
+      <c r="B58" s="154" t="s">
         <v>108</v>
       </c>
-      <c r="C58" s="162"/>
+      <c r="C58" s="154"/>
       <c r="D58" s="33"/>
       <c r="E58" s="33"/>
       <c r="F58" s="33"/>
@@ -6683,7 +6156,7 @@
       <c r="P58" s="47"/>
     </row>
     <row r="59" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="168"/>
+      <c r="A59" s="166"/>
       <c r="B59" s="29" t="s">
         <v>1</v>
       </c>
@@ -6705,7 +6178,7 @@
       <c r="P59" s="47"/>
     </row>
     <row r="60" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="168"/>
+      <c r="A60" s="166"/>
       <c r="B60" s="29" t="s">
         <v>2</v>
       </c>
@@ -6727,13 +6200,13 @@
       <c r="P60" s="47"/>
     </row>
     <row r="61" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="168">
+      <c r="A61" s="166">
         <v>14</v>
       </c>
-      <c r="B61" s="162" t="s">
+      <c r="B61" s="154" t="s">
         <v>111</v>
       </c>
-      <c r="C61" s="162"/>
+      <c r="C61" s="154"/>
       <c r="D61" s="33"/>
       <c r="E61" s="33"/>
       <c r="F61" s="33"/>
@@ -6749,7 +6222,7 @@
       <c r="P61" s="47"/>
     </row>
     <row r="62" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="168"/>
+      <c r="A62" s="166"/>
       <c r="B62" s="29" t="s">
         <v>1</v>
       </c>
@@ -6771,7 +6244,7 @@
       <c r="P62" s="47"/>
     </row>
     <row r="63" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="168"/>
+      <c r="A63" s="166"/>
       <c r="B63" s="29" t="s">
         <v>2</v>
       </c>
@@ -6793,13 +6266,13 @@
       <c r="P63" s="47"/>
     </row>
     <row r="64" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="168">
+      <c r="A64" s="166">
         <v>15</v>
       </c>
-      <c r="B64" s="162" t="s">
+      <c r="B64" s="154" t="s">
         <v>114</v>
       </c>
-      <c r="C64" s="162"/>
+      <c r="C64" s="154"/>
       <c r="D64" s="33"/>
       <c r="E64" s="33"/>
       <c r="F64" s="33"/>
@@ -6815,7 +6288,7 @@
       <c r="P64" s="47"/>
     </row>
     <row r="65" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="168"/>
+      <c r="A65" s="166"/>
       <c r="B65" s="29" t="s">
         <v>1</v>
       </c>
@@ -6837,7 +6310,7 @@
       <c r="P65" s="47"/>
     </row>
     <row r="66" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="168"/>
+      <c r="A66" s="166"/>
       <c r="B66" s="29" t="s">
         <v>2</v>
       </c>
@@ -6859,33 +6332,33 @@
       <c r="P66" s="47"/>
     </row>
     <row r="67" spans="1:16" s="20" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="162" t="s">
+      <c r="A67" s="154" t="s">
         <v>117</v>
       </c>
-      <c r="B67" s="162"/>
-      <c r="C67" s="162"/>
-      <c r="D67" s="162"/>
-      <c r="E67" s="162"/>
-      <c r="F67" s="162"/>
-      <c r="G67" s="162"/>
-      <c r="H67" s="162"/>
-      <c r="I67" s="162"/>
-      <c r="J67" s="162"/>
-      <c r="K67" s="162"/>
-      <c r="L67" s="162"/>
-      <c r="M67" s="162"/>
-      <c r="N67" s="162"/>
-      <c r="O67" s="162"/>
-      <c r="P67" s="162"/>
+      <c r="B67" s="154"/>
+      <c r="C67" s="154"/>
+      <c r="D67" s="154"/>
+      <c r="E67" s="154"/>
+      <c r="F67" s="154"/>
+      <c r="G67" s="154"/>
+      <c r="H67" s="154"/>
+      <c r="I67" s="154"/>
+      <c r="J67" s="154"/>
+      <c r="K67" s="154"/>
+      <c r="L67" s="154"/>
+      <c r="M67" s="154"/>
+      <c r="N67" s="154"/>
+      <c r="O67" s="154"/>
+      <c r="P67" s="154"/>
     </row>
     <row r="68" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="28">
         <v>16</v>
       </c>
-      <c r="B68" s="155" t="s">
+      <c r="B68" s="160" t="s">
         <v>118</v>
       </c>
-      <c r="C68" s="155"/>
+      <c r="C68" s="160"/>
       <c r="D68" s="33"/>
       <c r="E68" s="33"/>
       <c r="F68" s="33"/>
@@ -6904,10 +6377,10 @@
       <c r="A69" s="28">
         <v>17</v>
       </c>
-      <c r="B69" s="155" t="s">
+      <c r="B69" s="160" t="s">
         <v>119</v>
       </c>
-      <c r="C69" s="155"/>
+      <c r="C69" s="160"/>
       <c r="D69" s="33"/>
       <c r="E69" s="33"/>
       <c r="F69" s="28"/>
@@ -6926,10 +6399,10 @@
       <c r="A70" s="28">
         <v>18</v>
       </c>
-      <c r="B70" s="155" t="s">
+      <c r="B70" s="160" t="s">
         <v>33</v>
       </c>
-      <c r="C70" s="155"/>
+      <c r="C70" s="160"/>
       <c r="D70" s="33"/>
       <c r="E70" s="33"/>
       <c r="F70" s="33"/>
@@ -6948,10 +6421,10 @@
       <c r="A71" s="28">
         <v>19</v>
       </c>
-      <c r="B71" s="155" t="s">
+      <c r="B71" s="160" t="s">
         <v>120</v>
       </c>
-      <c r="C71" s="155"/>
+      <c r="C71" s="160"/>
       <c r="D71" s="33"/>
       <c r="E71" s="33"/>
       <c r="F71" s="33"/>
@@ -6970,10 +6443,10 @@
       <c r="A72" s="28">
         <v>20</v>
       </c>
-      <c r="B72" s="155" t="s">
+      <c r="B72" s="160" t="s">
         <v>34</v>
       </c>
-      <c r="C72" s="155"/>
+      <c r="C72" s="160"/>
       <c r="D72" s="33"/>
       <c r="E72" s="33"/>
       <c r="F72" s="33"/>
@@ -6992,10 +6465,10 @@
       <c r="A73" s="28">
         <v>21</v>
       </c>
-      <c r="B73" s="155" t="s">
+      <c r="B73" s="160" t="s">
         <v>61</v>
       </c>
-      <c r="C73" s="155"/>
+      <c r="C73" s="160"/>
       <c r="D73" s="33"/>
       <c r="E73" s="33"/>
       <c r="F73" s="33"/>
@@ -7014,10 +6487,10 @@
       <c r="A74" s="28">
         <v>1</v>
       </c>
-      <c r="B74" s="155" t="s">
+      <c r="B74" s="160" t="s">
         <v>206</v>
       </c>
-      <c r="C74" s="155"/>
+      <c r="C74" s="160"/>
       <c r="D74" s="33">
         <v>10</v>
       </c>
@@ -7065,10 +6538,10 @@
       <c r="A75" s="28">
         <v>23</v>
       </c>
-      <c r="B75" s="155" t="s">
+      <c r="B75" s="160" t="s">
         <v>121</v>
       </c>
-      <c r="C75" s="155"/>
+      <c r="C75" s="160"/>
       <c r="D75" s="33"/>
       <c r="E75" s="33"/>
       <c r="F75" s="33"/>
@@ -7087,10 +6560,10 @@
       <c r="A76" s="28">
         <v>24</v>
       </c>
-      <c r="B76" s="155" t="s">
+      <c r="B76" s="160" t="s">
         <v>122</v>
       </c>
-      <c r="C76" s="155"/>
+      <c r="C76" s="160"/>
       <c r="D76" s="33"/>
       <c r="E76" s="33"/>
       <c r="F76" s="33"/>
@@ -7106,11 +6579,11 @@
       <c r="P76" s="47"/>
     </row>
     <row r="77" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="162" t="s">
+      <c r="A77" s="154" t="s">
         <v>123</v>
       </c>
-      <c r="B77" s="162"/>
-      <c r="C77" s="162"/>
+      <c r="B77" s="154"/>
+      <c r="C77" s="154"/>
       <c r="D77" s="33"/>
       <c r="E77" s="33"/>
       <c r="F77" s="33"/>
@@ -7129,10 +6602,10 @@
       <c r="A78" s="28">
         <v>25</v>
       </c>
-      <c r="B78" s="155" t="s">
+      <c r="B78" s="160" t="s">
         <v>35</v>
       </c>
-      <c r="C78" s="155"/>
+      <c r="C78" s="160"/>
       <c r="D78" s="33"/>
       <c r="E78" s="33"/>
       <c r="F78" s="33"/>
@@ -7151,10 +6624,10 @@
       <c r="A79" s="28">
         <v>26</v>
       </c>
-      <c r="B79" s="155" t="s">
+      <c r="B79" s="160" t="s">
         <v>124</v>
       </c>
-      <c r="C79" s="155"/>
+      <c r="C79" s="160"/>
       <c r="D79" s="33"/>
       <c r="E79" s="33"/>
       <c r="F79" s="33"/>
@@ -7173,10 +6646,10 @@
       <c r="A80" s="28">
         <v>27</v>
       </c>
-      <c r="B80" s="155" t="s">
+      <c r="B80" s="160" t="s">
         <v>125</v>
       </c>
-      <c r="C80" s="155"/>
+      <c r="C80" s="160"/>
       <c r="D80" s="33"/>
       <c r="E80" s="33"/>
       <c r="F80" s="33"/>
@@ -7195,10 +6668,10 @@
       <c r="A81" s="28">
         <v>28</v>
       </c>
-      <c r="B81" s="155" t="s">
+      <c r="B81" s="160" t="s">
         <v>126</v>
       </c>
-      <c r="C81" s="155"/>
+      <c r="C81" s="160"/>
       <c r="D81" s="33"/>
       <c r="E81" s="33"/>
       <c r="F81" s="33"/>
@@ -7217,10 +6690,10 @@
       <c r="A82" s="28">
         <v>29</v>
       </c>
-      <c r="B82" s="155" t="s">
+      <c r="B82" s="160" t="s">
         <v>127</v>
       </c>
-      <c r="C82" s="155"/>
+      <c r="C82" s="160"/>
       <c r="D82" s="33"/>
       <c r="E82" s="33"/>
       <c r="F82" s="33"/>
@@ -7239,10 +6712,10 @@
       <c r="A83" s="28">
         <v>30</v>
       </c>
-      <c r="B83" s="155" t="s">
+      <c r="B83" s="160" t="s">
         <v>128</v>
       </c>
-      <c r="C83" s="155"/>
+      <c r="C83" s="160"/>
       <c r="D83" s="33"/>
       <c r="E83" s="33"/>
       <c r="F83" s="33"/>
@@ -7258,11 +6731,11 @@
       <c r="P83" s="47"/>
     </row>
     <row r="84" spans="1:16" s="20" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="162" t="s">
+      <c r="A84" s="154" t="s">
         <v>129</v>
       </c>
-      <c r="B84" s="162"/>
-      <c r="C84" s="162"/>
+      <c r="B84" s="154"/>
+      <c r="C84" s="154"/>
       <c r="D84" s="47"/>
       <c r="E84" s="47"/>
       <c r="F84" s="47"/>
@@ -7281,10 +6754,10 @@
       <c r="A85" s="28">
         <v>31</v>
       </c>
-      <c r="B85" s="156" t="s">
+      <c r="B85" s="155" t="s">
         <v>130</v>
       </c>
-      <c r="C85" s="156"/>
+      <c r="C85" s="155"/>
       <c r="D85" s="33"/>
       <c r="E85" s="33"/>
       <c r="F85" s="33"/>
@@ -7303,10 +6776,10 @@
       <c r="A86" s="7">
         <v>32</v>
       </c>
-      <c r="B86" s="156" t="s">
+      <c r="B86" s="155" t="s">
         <v>141</v>
       </c>
-      <c r="C86" s="156"/>
+      <c r="C86" s="155"/>
       <c r="D86" s="33"/>
       <c r="E86" s="33"/>
       <c r="F86" s="33"/>
@@ -7325,10 +6798,10 @@
       <c r="A87" s="28">
         <v>33</v>
       </c>
-      <c r="B87" s="156" t="s">
+      <c r="B87" s="155" t="s">
         <v>131</v>
       </c>
-      <c r="C87" s="156"/>
+      <c r="C87" s="155"/>
       <c r="D87" s="33"/>
       <c r="E87" s="33"/>
       <c r="F87" s="33"/>
@@ -7347,10 +6820,10 @@
       <c r="A88" s="7">
         <v>34</v>
       </c>
-      <c r="B88" s="156" t="s">
+      <c r="B88" s="155" t="s">
         <v>142</v>
       </c>
-      <c r="C88" s="156"/>
+      <c r="C88" s="155"/>
       <c r="D88" s="33"/>
       <c r="E88" s="33"/>
       <c r="F88" s="33"/>
@@ -7369,10 +6842,10 @@
       <c r="A89" s="28">
         <v>35</v>
       </c>
-      <c r="B89" s="156" t="s">
+      <c r="B89" s="155" t="s">
         <v>132</v>
       </c>
-      <c r="C89" s="156"/>
+      <c r="C89" s="155"/>
       <c r="D89" s="33"/>
       <c r="E89" s="33"/>
       <c r="F89" s="33"/>
@@ -7391,10 +6864,10 @@
       <c r="A90" s="7">
         <v>36</v>
       </c>
-      <c r="B90" s="156" t="s">
+      <c r="B90" s="155" t="s">
         <v>133</v>
       </c>
-      <c r="C90" s="156"/>
+      <c r="C90" s="155"/>
       <c r="D90" s="33"/>
       <c r="E90" s="33"/>
       <c r="F90" s="33"/>
@@ -7413,10 +6886,10 @@
       <c r="A91" s="28">
         <v>37</v>
       </c>
-      <c r="B91" s="156" t="s">
+      <c r="B91" s="155" t="s">
         <v>134</v>
       </c>
-      <c r="C91" s="156"/>
+      <c r="C91" s="155"/>
       <c r="D91" s="33"/>
       <c r="E91" s="33"/>
       <c r="F91" s="33"/>
@@ -7435,10 +6908,10 @@
       <c r="A92" s="7">
         <v>38</v>
       </c>
-      <c r="B92" s="156" t="s">
+      <c r="B92" s="155" t="s">
         <v>135</v>
       </c>
-      <c r="C92" s="156"/>
+      <c r="C92" s="155"/>
       <c r="D92" s="33"/>
       <c r="E92" s="33"/>
       <c r="F92" s="33"/>
@@ -7457,10 +6930,10 @@
       <c r="A93" s="28">
         <v>39</v>
       </c>
-      <c r="B93" s="156" t="s">
+      <c r="B93" s="155" t="s">
         <v>136</v>
       </c>
-      <c r="C93" s="156"/>
+      <c r="C93" s="155"/>
       <c r="D93" s="33"/>
       <c r="E93" s="33"/>
       <c r="F93" s="33"/>
@@ -7479,10 +6952,10 @@
       <c r="A94" s="7">
         <v>40</v>
       </c>
-      <c r="B94" s="156" t="s">
+      <c r="B94" s="155" t="s">
         <v>39</v>
       </c>
-      <c r="C94" s="156"/>
+      <c r="C94" s="155"/>
       <c r="D94" s="33"/>
       <c r="E94" s="33"/>
       <c r="F94" s="33"/>
@@ -7501,10 +6974,10 @@
       <c r="A95" s="28">
         <v>41</v>
       </c>
-      <c r="B95" s="156" t="s">
+      <c r="B95" s="155" t="s">
         <v>137</v>
       </c>
-      <c r="C95" s="156"/>
+      <c r="C95" s="155"/>
       <c r="D95" s="33"/>
       <c r="E95" s="33"/>
       <c r="F95" s="33"/>
@@ -7523,10 +6996,10 @@
       <c r="A96" s="7">
         <v>42</v>
       </c>
-      <c r="B96" s="156" t="s">
+      <c r="B96" s="155" t="s">
         <v>40</v>
       </c>
-      <c r="C96" s="156"/>
+      <c r="C96" s="155"/>
       <c r="D96" s="33"/>
       <c r="E96" s="33"/>
       <c r="F96" s="33"/>
@@ -7545,10 +7018,10 @@
       <c r="A97" s="28">
         <v>43</v>
       </c>
-      <c r="B97" s="156" t="s">
+      <c r="B97" s="155" t="s">
         <v>138</v>
       </c>
-      <c r="C97" s="156"/>
+      <c r="C97" s="155"/>
       <c r="D97" s="33"/>
       <c r="E97" s="33"/>
       <c r="F97" s="33"/>
@@ -7567,10 +7040,10 @@
       <c r="A98" s="7">
         <v>44</v>
       </c>
-      <c r="B98" s="156" t="s">
+      <c r="B98" s="155" t="s">
         <v>41</v>
       </c>
-      <c r="C98" s="156"/>
+      <c r="C98" s="155"/>
       <c r="D98" s="33"/>
       <c r="E98" s="33"/>
       <c r="F98" s="33"/>
@@ -7589,10 +7062,10 @@
       <c r="A99" s="28">
         <v>45</v>
       </c>
-      <c r="B99" s="156" t="s">
+      <c r="B99" s="155" t="s">
         <v>42</v>
       </c>
-      <c r="C99" s="156"/>
+      <c r="C99" s="155"/>
       <c r="D99" s="33"/>
       <c r="E99" s="33"/>
       <c r="F99" s="33"/>
@@ -7611,10 +7084,10 @@
       <c r="A100" s="7">
         <v>46</v>
       </c>
-      <c r="B100" s="156" t="s">
+      <c r="B100" s="155" t="s">
         <v>43</v>
       </c>
-      <c r="C100" s="156"/>
+      <c r="C100" s="155"/>
       <c r="D100" s="33"/>
       <c r="E100" s="33"/>
       <c r="F100" s="33"/>
@@ -7633,10 +7106,10 @@
       <c r="A101" s="28">
         <v>47</v>
       </c>
-      <c r="B101" s="156" t="s">
+      <c r="B101" s="155" t="s">
         <v>139</v>
       </c>
-      <c r="C101" s="156"/>
+      <c r="C101" s="155"/>
       <c r="D101" s="33"/>
       <c r="E101" s="33"/>
       <c r="F101" s="33"/>
@@ -7655,10 +7128,10 @@
       <c r="A102" s="7">
         <v>2</v>
       </c>
-      <c r="B102" s="155" t="s">
+      <c r="B102" s="160" t="s">
         <v>207</v>
       </c>
-      <c r="C102" s="155"/>
+      <c r="C102" s="160"/>
       <c r="D102" s="33">
         <v>4</v>
       </c>
@@ -7705,10 +7178,10 @@
       <c r="A103" s="7">
         <v>1</v>
       </c>
-      <c r="B103" s="156" t="s">
+      <c r="B103" s="155" t="s">
         <v>208</v>
       </c>
-      <c r="C103" s="156"/>
+      <c r="C103" s="155"/>
       <c r="D103" s="33">
         <v>0</v>
       </c>
@@ -7748,33 +7221,33 @@
       <c r="P103" s="63"/>
     </row>
     <row r="104" spans="1:16" s="20" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="162" t="s">
+      <c r="A104" s="154" t="s">
         <v>129</v>
       </c>
-      <c r="B104" s="162"/>
-      <c r="C104" s="162"/>
-      <c r="D104" s="162"/>
-      <c r="E104" s="162"/>
-      <c r="F104" s="162"/>
-      <c r="G104" s="162"/>
-      <c r="H104" s="162"/>
-      <c r="I104" s="162"/>
-      <c r="J104" s="162"/>
-      <c r="K104" s="162"/>
-      <c r="L104" s="162"/>
-      <c r="M104" s="162"/>
-      <c r="N104" s="162"/>
-      <c r="O104" s="162"/>
-      <c r="P104" s="162"/>
+      <c r="B104" s="154"/>
+      <c r="C104" s="154"/>
+      <c r="D104" s="154"/>
+      <c r="E104" s="154"/>
+      <c r="F104" s="154"/>
+      <c r="G104" s="154"/>
+      <c r="H104" s="154"/>
+      <c r="I104" s="154"/>
+      <c r="J104" s="154"/>
+      <c r="K104" s="154"/>
+      <c r="L104" s="154"/>
+      <c r="M104" s="154"/>
+      <c r="N104" s="154"/>
+      <c r="O104" s="154"/>
+      <c r="P104" s="154"/>
     </row>
     <row r="105" spans="1:16" s="57" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="7">
         <v>1</v>
       </c>
-      <c r="B105" s="156" t="s">
+      <c r="B105" s="155" t="s">
         <v>209</v>
       </c>
-      <c r="C105" s="156"/>
+      <c r="C105" s="155"/>
       <c r="D105" s="33">
         <v>8</v>
       </c>
@@ -7818,10 +7291,10 @@
       <c r="A106" s="7">
         <v>2</v>
       </c>
-      <c r="B106" s="156" t="s">
+      <c r="B106" s="155" t="s">
         <v>210</v>
       </c>
-      <c r="C106" s="156"/>
+      <c r="C106" s="155"/>
       <c r="D106" s="33">
         <v>2</v>
       </c>
@@ -7862,33 +7335,33 @@
       <c r="P106" s="47"/>
     </row>
     <row r="107" spans="1:16" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="162" t="s">
+      <c r="A107" s="154" t="s">
         <v>144</v>
       </c>
-      <c r="B107" s="162"/>
-      <c r="C107" s="162"/>
-      <c r="D107" s="162"/>
-      <c r="E107" s="162"/>
-      <c r="F107" s="162"/>
-      <c r="G107" s="162"/>
-      <c r="H107" s="162"/>
-      <c r="I107" s="162"/>
-      <c r="J107" s="162"/>
-      <c r="K107" s="162"/>
-      <c r="L107" s="162"/>
-      <c r="M107" s="162"/>
-      <c r="N107" s="162"/>
-      <c r="O107" s="162"/>
-      <c r="P107" s="162"/>
+      <c r="B107" s="154"/>
+      <c r="C107" s="154"/>
+      <c r="D107" s="154"/>
+      <c r="E107" s="154"/>
+      <c r="F107" s="154"/>
+      <c r="G107" s="154"/>
+      <c r="H107" s="154"/>
+      <c r="I107" s="154"/>
+      <c r="J107" s="154"/>
+      <c r="K107" s="154"/>
+      <c r="L107" s="154"/>
+      <c r="M107" s="154"/>
+      <c r="N107" s="154"/>
+      <c r="O107" s="154"/>
+      <c r="P107" s="154"/>
     </row>
     <row r="108" spans="1:16" s="49" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="7">
         <v>1</v>
       </c>
-      <c r="B108" s="156" t="s">
+      <c r="B108" s="155" t="s">
         <v>211</v>
       </c>
-      <c r="C108" s="156"/>
+      <c r="C108" s="155"/>
       <c r="D108" s="33">
         <v>35</v>
       </c>
@@ -7937,132 +7410,132 @@
       <c r="A109" s="30">
         <v>2</v>
       </c>
-      <c r="B109" s="175" t="s">
+      <c r="B109" s="153" t="s">
         <v>212</v>
       </c>
-      <c r="C109" s="175"/>
-      <c r="D109" s="128">
+      <c r="C109" s="153"/>
+      <c r="D109" s="127">
         <v>27</v>
       </c>
-      <c r="E109" s="128">
+      <c r="E109" s="127">
         <v>24</v>
       </c>
-      <c r="F109" s="128">
-        <v>0</v>
-      </c>
-      <c r="G109" s="128">
-        <v>0</v>
-      </c>
-      <c r="H109" s="128">
-        <v>0</v>
-      </c>
-      <c r="I109" s="128">
-        <v>0</v>
-      </c>
-      <c r="J109" s="128">
-        <v>0</v>
-      </c>
-      <c r="K109" s="129">
+      <c r="F109" s="127">
+        <v>0</v>
+      </c>
+      <c r="G109" s="127">
+        <v>0</v>
+      </c>
+      <c r="H109" s="127">
+        <v>0</v>
+      </c>
+      <c r="I109" s="127">
+        <v>0</v>
+      </c>
+      <c r="J109" s="127">
+        <v>0</v>
+      </c>
+      <c r="K109" s="128">
         <v>24</v>
       </c>
-      <c r="L109" s="130">
+      <c r="L109" s="129">
         <f>IF(E109=0,"-",(I109/E109))</f>
         <v>0</v>
       </c>
-      <c r="M109" s="130">
+      <c r="M109" s="129">
         <f>IF(E109=0,"-",(J109/E109))</f>
         <v>0</v>
       </c>
-      <c r="N109" s="130">
+      <c r="N109" s="129">
         <f>IF(E109=0,"-",(K109/E109))</f>
         <v>1</v>
       </c>
-      <c r="O109" s="130">
+      <c r="O109" s="129">
         <f>IF(E109=0,"-",(M109+N109))</f>
         <v>1</v>
       </c>
-      <c r="P109" s="131"/>
+      <c r="P109" s="130"/>
     </row>
     <row r="110" spans="1:16" s="20" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A110" s="7">
         <v>3</v>
       </c>
-      <c r="B110" s="175" t="s">
+      <c r="B110" s="153" t="s">
         <v>145</v>
       </c>
-      <c r="C110" s="175"/>
-      <c r="D110" s="128"/>
-      <c r="E110" s="128"/>
-      <c r="F110" s="128"/>
-      <c r="G110" s="128"/>
-      <c r="H110" s="128"/>
-      <c r="I110" s="128"/>
-      <c r="J110" s="128"/>
-      <c r="K110" s="129"/>
-      <c r="L110" s="130"/>
-      <c r="M110" s="130"/>
-      <c r="N110" s="130"/>
-      <c r="O110" s="130"/>
-      <c r="P110" s="131"/>
+      <c r="C110" s="153"/>
+      <c r="D110" s="127"/>
+      <c r="E110" s="127"/>
+      <c r="F110" s="127"/>
+      <c r="G110" s="127"/>
+      <c r="H110" s="127"/>
+      <c r="I110" s="127"/>
+      <c r="J110" s="127"/>
+      <c r="K110" s="128"/>
+      <c r="L110" s="129"/>
+      <c r="M110" s="129"/>
+      <c r="N110" s="129"/>
+      <c r="O110" s="129"/>
+      <c r="P110" s="130"/>
     </row>
     <row r="111" spans="1:16" s="20" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A111" s="30">
         <v>4</v>
       </c>
-      <c r="B111" s="175" t="s">
+      <c r="B111" s="153" t="s">
         <v>213</v>
       </c>
-      <c r="C111" s="175"/>
-      <c r="D111" s="128">
+      <c r="C111" s="153"/>
+      <c r="D111" s="127">
         <v>5</v>
       </c>
-      <c r="E111" s="128">
+      <c r="E111" s="127">
         <v>2</v>
       </c>
-      <c r="F111" s="128">
-        <v>0</v>
-      </c>
-      <c r="G111" s="128">
-        <v>0</v>
-      </c>
-      <c r="H111" s="128">
-        <v>0</v>
-      </c>
-      <c r="I111" s="128">
-        <v>0</v>
-      </c>
-      <c r="J111" s="128">
-        <v>0</v>
-      </c>
-      <c r="K111" s="129">
+      <c r="F111" s="127">
+        <v>0</v>
+      </c>
+      <c r="G111" s="127">
+        <v>0</v>
+      </c>
+      <c r="H111" s="127">
+        <v>0</v>
+      </c>
+      <c r="I111" s="127">
+        <v>0</v>
+      </c>
+      <c r="J111" s="127">
+        <v>0</v>
+      </c>
+      <c r="K111" s="128">
         <v>2</v>
       </c>
-      <c r="L111" s="130">
+      <c r="L111" s="129">
         <f>IF(E111=0,"-",(I111/E111))</f>
         <v>0</v>
       </c>
-      <c r="M111" s="130">
+      <c r="M111" s="129">
         <f>IF(E111=0,"-",(J111/E111))</f>
         <v>0</v>
       </c>
-      <c r="N111" s="130">
+      <c r="N111" s="129">
         <f>IF(E111=0,"-",(K111/E111))</f>
         <v>1</v>
       </c>
-      <c r="O111" s="130">
+      <c r="O111" s="129">
         <f>IF(E111=0,"-",(M111+N111))</f>
         <v>1</v>
       </c>
-      <c r="P111" s="131"/>
+      <c r="P111" s="130"/>
     </row>
     <row r="112" spans="1:16" s="49" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A112" s="7">
         <v>5</v>
       </c>
-      <c r="B112" s="156" t="s">
+      <c r="B112" s="155" t="s">
         <v>214</v>
       </c>
-      <c r="C112" s="156"/>
+      <c r="C112" s="155"/>
       <c r="D112" s="33">
         <v>95</v>
       </c>
@@ -8104,246 +7577,246 @@
         <f>IF(E112=0,"-",(M112+N112))</f>
         <v>1</v>
       </c>
-      <c r="P112" s="79"/>
-    </row>
-    <row r="113" spans="1:16" s="115" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P112" s="78"/>
+    </row>
+    <row r="113" spans="1:16" s="114" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="30">
         <v>6</v>
       </c>
-      <c r="B113" s="164" t="s">
+      <c r="B113" s="159" t="s">
         <v>216</v>
       </c>
-      <c r="C113" s="164"/>
-      <c r="D113" s="122">
+      <c r="C113" s="159"/>
+      <c r="D113" s="121">
         <v>156</v>
       </c>
-      <c r="E113" s="122" t="s">
+      <c r="E113" s="121" t="s">
         <v>159</v>
       </c>
-      <c r="F113" s="121">
-        <v>0</v>
-      </c>
-      <c r="G113" s="121">
-        <v>0</v>
-      </c>
-      <c r="H113" s="121">
-        <v>0</v>
-      </c>
-      <c r="I113" s="121">
-        <v>0</v>
-      </c>
-      <c r="J113" s="121">
-        <v>0</v>
-      </c>
-      <c r="K113" s="123">
+      <c r="F113" s="120">
+        <v>0</v>
+      </c>
+      <c r="G113" s="120">
+        <v>0</v>
+      </c>
+      <c r="H113" s="120">
+        <v>0</v>
+      </c>
+      <c r="I113" s="120">
+        <v>0</v>
+      </c>
+      <c r="J113" s="120">
+        <v>0</v>
+      </c>
+      <c r="K113" s="122">
         <v>191</v>
       </c>
-      <c r="L113" s="124">
-        <v>0</v>
-      </c>
-      <c r="M113" s="124">
-        <v>0</v>
-      </c>
-      <c r="N113" s="124">
-        <v>1</v>
-      </c>
-      <c r="O113" s="124">
-        <v>1</v>
-      </c>
-      <c r="P113" s="125"/>
+      <c r="L113" s="123">
+        <v>0</v>
+      </c>
+      <c r="M113" s="123">
+        <v>0</v>
+      </c>
+      <c r="N113" s="123">
+        <v>1</v>
+      </c>
+      <c r="O113" s="123">
+        <v>1</v>
+      </c>
+      <c r="P113" s="124"/>
     </row>
     <row r="114" spans="1:16" s="20" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="7">
         <v>7</v>
       </c>
-      <c r="B114" s="164" t="s">
+      <c r="B114" s="159" t="s">
         <v>215</v>
       </c>
-      <c r="C114" s="164"/>
-      <c r="D114" s="122">
-        <v>1</v>
-      </c>
-      <c r="E114" s="122">
-        <v>1</v>
-      </c>
-      <c r="F114" s="121">
-        <v>0</v>
-      </c>
-      <c r="G114" s="121">
-        <v>0</v>
-      </c>
-      <c r="H114" s="121">
-        <v>0</v>
-      </c>
-      <c r="I114" s="121">
-        <v>0</v>
-      </c>
-      <c r="J114" s="121">
-        <v>0</v>
-      </c>
-      <c r="K114" s="123">
-        <v>1</v>
-      </c>
-      <c r="L114" s="124">
-        <v>0</v>
-      </c>
-      <c r="M114" s="124">
-        <v>0</v>
-      </c>
-      <c r="N114" s="124">
-        <v>1</v>
-      </c>
-      <c r="O114" s="124">
-        <v>1</v>
-      </c>
-      <c r="P114" s="125"/>
+      <c r="C114" s="159"/>
+      <c r="D114" s="121">
+        <v>1</v>
+      </c>
+      <c r="E114" s="121">
+        <v>1</v>
+      </c>
+      <c r="F114" s="120">
+        <v>0</v>
+      </c>
+      <c r="G114" s="120">
+        <v>0</v>
+      </c>
+      <c r="H114" s="120">
+        <v>0</v>
+      </c>
+      <c r="I114" s="120">
+        <v>0</v>
+      </c>
+      <c r="J114" s="120">
+        <v>0</v>
+      </c>
+      <c r="K114" s="122">
+        <v>1</v>
+      </c>
+      <c r="L114" s="123">
+        <v>0</v>
+      </c>
+      <c r="M114" s="123">
+        <v>0</v>
+      </c>
+      <c r="N114" s="123">
+        <v>1</v>
+      </c>
+      <c r="O114" s="123">
+        <v>1</v>
+      </c>
+      <c r="P114" s="124"/>
     </row>
     <row r="115" spans="1:16" s="20" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="30">
         <v>8</v>
       </c>
-      <c r="B115" s="164" t="s">
+      <c r="B115" s="159" t="s">
         <v>217</v>
       </c>
-      <c r="C115" s="164"/>
-      <c r="D115" s="122">
+      <c r="C115" s="159"/>
+      <c r="D115" s="121">
         <v>5</v>
       </c>
-      <c r="E115" s="122">
+      <c r="E115" s="121">
         <v>4</v>
       </c>
-      <c r="F115" s="121">
-        <v>0</v>
-      </c>
-      <c r="G115" s="121">
-        <v>0</v>
-      </c>
-      <c r="H115" s="121">
-        <v>0</v>
-      </c>
-      <c r="I115" s="121">
-        <v>0</v>
-      </c>
-      <c r="J115" s="121">
-        <v>0</v>
-      </c>
-      <c r="K115" s="123">
+      <c r="F115" s="120">
+        <v>0</v>
+      </c>
+      <c r="G115" s="120">
+        <v>0</v>
+      </c>
+      <c r="H115" s="120">
+        <v>0</v>
+      </c>
+      <c r="I115" s="120">
+        <v>0</v>
+      </c>
+      <c r="J115" s="120">
+        <v>0</v>
+      </c>
+      <c r="K115" s="122">
         <v>4</v>
       </c>
-      <c r="L115" s="124">
-        <v>0</v>
-      </c>
-      <c r="M115" s="124">
-        <v>0</v>
-      </c>
-      <c r="N115" s="124">
-        <v>1</v>
-      </c>
-      <c r="O115" s="124">
-        <v>1</v>
-      </c>
-      <c r="P115" s="125"/>
+      <c r="L115" s="123">
+        <v>0</v>
+      </c>
+      <c r="M115" s="123">
+        <v>0</v>
+      </c>
+      <c r="N115" s="123">
+        <v>1</v>
+      </c>
+      <c r="O115" s="123">
+        <v>1</v>
+      </c>
+      <c r="P115" s="124"/>
     </row>
     <row r="116" spans="1:16" s="20" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="7">
         <v>9</v>
       </c>
-      <c r="B116" s="164" t="s">
+      <c r="B116" s="159" t="s">
         <v>218</v>
       </c>
-      <c r="C116" s="164"/>
-      <c r="D116" s="122">
+      <c r="C116" s="159"/>
+      <c r="D116" s="121">
         <v>6</v>
       </c>
-      <c r="E116" s="122">
+      <c r="E116" s="121">
         <v>4</v>
       </c>
-      <c r="F116" s="121">
-        <v>0</v>
-      </c>
-      <c r="G116" s="121">
-        <v>0</v>
-      </c>
-      <c r="H116" s="121">
-        <v>0</v>
-      </c>
-      <c r="I116" s="121">
-        <v>0</v>
-      </c>
-      <c r="J116" s="121">
-        <v>0</v>
-      </c>
-      <c r="K116" s="123">
+      <c r="F116" s="120">
+        <v>0</v>
+      </c>
+      <c r="G116" s="120">
+        <v>0</v>
+      </c>
+      <c r="H116" s="120">
+        <v>0</v>
+      </c>
+      <c r="I116" s="120">
+        <v>0</v>
+      </c>
+      <c r="J116" s="120">
+        <v>0</v>
+      </c>
+      <c r="K116" s="122">
         <v>4</v>
       </c>
-      <c r="L116" s="124">
-        <v>0</v>
-      </c>
-      <c r="M116" s="124">
-        <v>0</v>
-      </c>
-      <c r="N116" s="124">
-        <v>1</v>
-      </c>
-      <c r="O116" s="124">
-        <v>1</v>
-      </c>
-      <c r="P116" s="125"/>
+      <c r="L116" s="123">
+        <v>0</v>
+      </c>
+      <c r="M116" s="123">
+        <v>0</v>
+      </c>
+      <c r="N116" s="123">
+        <v>1</v>
+      </c>
+      <c r="O116" s="123">
+        <v>1</v>
+      </c>
+      <c r="P116" s="124"/>
     </row>
     <row r="117" spans="1:16" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="30">
         <v>10</v>
       </c>
-      <c r="B117" s="164" t="s">
+      <c r="B117" s="159" t="s">
         <v>219</v>
       </c>
-      <c r="C117" s="164"/>
-      <c r="D117" s="122">
-        <v>1</v>
-      </c>
-      <c r="E117" s="122">
-        <v>1</v>
-      </c>
-      <c r="F117" s="121">
-        <v>0</v>
-      </c>
-      <c r="G117" s="121">
-        <v>0</v>
-      </c>
-      <c r="H117" s="121">
-        <v>0</v>
-      </c>
-      <c r="I117" s="121">
-        <v>0</v>
-      </c>
-      <c r="J117" s="121">
-        <v>0</v>
-      </c>
-      <c r="K117" s="123">
-        <v>1</v>
-      </c>
-      <c r="L117" s="124">
-        <v>0</v>
-      </c>
-      <c r="M117" s="124">
-        <v>0</v>
-      </c>
-      <c r="N117" s="124">
-        <v>1</v>
-      </c>
-      <c r="O117" s="124">
-        <v>1</v>
-      </c>
-      <c r="P117" s="125"/>
+      <c r="C117" s="159"/>
+      <c r="D117" s="121">
+        <v>1</v>
+      </c>
+      <c r="E117" s="121">
+        <v>1</v>
+      </c>
+      <c r="F117" s="120">
+        <v>0</v>
+      </c>
+      <c r="G117" s="120">
+        <v>0</v>
+      </c>
+      <c r="H117" s="120">
+        <v>0</v>
+      </c>
+      <c r="I117" s="120">
+        <v>0</v>
+      </c>
+      <c r="J117" s="120">
+        <v>0</v>
+      </c>
+      <c r="K117" s="122">
+        <v>1</v>
+      </c>
+      <c r="L117" s="123">
+        <v>0</v>
+      </c>
+      <c r="M117" s="123">
+        <v>0</v>
+      </c>
+      <c r="N117" s="123">
+        <v>1</v>
+      </c>
+      <c r="O117" s="123">
+        <v>1</v>
+      </c>
+      <c r="P117" s="124"/>
     </row>
     <row r="118" spans="1:16" s="20" customFormat="1" ht="85.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="7">
         <v>11</v>
       </c>
-      <c r="B118" s="155" t="s">
+      <c r="B118" s="160" t="s">
         <v>220</v>
       </c>
-      <c r="C118" s="155"/>
+      <c r="C118" s="160"/>
       <c r="D118" s="33">
         <v>0</v>
       </c>
@@ -8385,7 +7858,7 @@
         <f>IF(E118=0,"-",(M118+N118))</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="P118" s="140" t="s">
+      <c r="P118" s="138" t="s">
         <v>161</v>
       </c>
     </row>
@@ -8393,88 +7866,88 @@
       <c r="A119" s="30">
         <v>12</v>
       </c>
-      <c r="B119" s="165"/>
-      <c r="C119" s="165"/>
-      <c r="D119" s="122"/>
-      <c r="E119" s="122"/>
-      <c r="F119" s="122"/>
-      <c r="G119" s="122"/>
-      <c r="H119" s="121"/>
-      <c r="I119" s="121"/>
-      <c r="J119" s="122"/>
-      <c r="K119" s="126"/>
-      <c r="L119" s="127"/>
-      <c r="M119" s="127"/>
-      <c r="N119" s="127"/>
-      <c r="O119" s="127"/>
-      <c r="P119" s="125"/>
+      <c r="B119" s="158"/>
+      <c r="C119" s="158"/>
+      <c r="D119" s="121"/>
+      <c r="E119" s="121"/>
+      <c r="F119" s="121"/>
+      <c r="G119" s="121"/>
+      <c r="H119" s="120"/>
+      <c r="I119" s="120"/>
+      <c r="J119" s="121"/>
+      <c r="K119" s="125"/>
+      <c r="L119" s="126"/>
+      <c r="M119" s="126"/>
+      <c r="N119" s="126"/>
+      <c r="O119" s="126"/>
+      <c r="P119" s="124"/>
     </row>
     <row r="120" spans="1:16" s="20" customFormat="1" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="7">
         <v>13</v>
       </c>
-      <c r="B120" s="165"/>
-      <c r="C120" s="165"/>
-      <c r="D120" s="122"/>
-      <c r="E120" s="122"/>
-      <c r="F120" s="122"/>
-      <c r="G120" s="122"/>
-      <c r="H120" s="121"/>
-      <c r="I120" s="121"/>
-      <c r="J120" s="122"/>
-      <c r="K120" s="126"/>
-      <c r="L120" s="127"/>
-      <c r="M120" s="127"/>
-      <c r="N120" s="127"/>
-      <c r="O120" s="127"/>
-      <c r="P120" s="125"/>
+      <c r="B120" s="158"/>
+      <c r="C120" s="158"/>
+      <c r="D120" s="121"/>
+      <c r="E120" s="121"/>
+      <c r="F120" s="121"/>
+      <c r="G120" s="121"/>
+      <c r="H120" s="120"/>
+      <c r="I120" s="120"/>
+      <c r="J120" s="121"/>
+      <c r="K120" s="125"/>
+      <c r="L120" s="126"/>
+      <c r="M120" s="126"/>
+      <c r="N120" s="126"/>
+      <c r="O120" s="126"/>
+      <c r="P120" s="124"/>
     </row>
     <row r="121" spans="1:16" s="20" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="30">
         <v>14</v>
       </c>
-      <c r="B121" s="165"/>
-      <c r="C121" s="165"/>
-      <c r="D121" s="122"/>
-      <c r="E121" s="122"/>
-      <c r="F121" s="122"/>
-      <c r="G121" s="122"/>
-      <c r="H121" s="121"/>
-      <c r="I121" s="121"/>
-      <c r="J121" s="122"/>
-      <c r="K121" s="126"/>
-      <c r="L121" s="127"/>
-      <c r="M121" s="127"/>
-      <c r="N121" s="127"/>
-      <c r="O121" s="127"/>
-      <c r="P121" s="125"/>
+      <c r="B121" s="158"/>
+      <c r="C121" s="158"/>
+      <c r="D121" s="121"/>
+      <c r="E121" s="121"/>
+      <c r="F121" s="121"/>
+      <c r="G121" s="121"/>
+      <c r="H121" s="120"/>
+      <c r="I121" s="120"/>
+      <c r="J121" s="121"/>
+      <c r="K121" s="125"/>
+      <c r="L121" s="126"/>
+      <c r="M121" s="126"/>
+      <c r="N121" s="126"/>
+      <c r="O121" s="126"/>
+      <c r="P121" s="124"/>
     </row>
     <row r="122" spans="1:16" s="20" customFormat="1" ht="27.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="7">
         <v>15</v>
       </c>
-      <c r="B122" s="165"/>
-      <c r="C122" s="165"/>
-      <c r="D122" s="122"/>
-      <c r="E122" s="122"/>
-      <c r="F122" s="122"/>
-      <c r="G122" s="122"/>
-      <c r="H122" s="121"/>
-      <c r="I122" s="121"/>
-      <c r="J122" s="122"/>
-      <c r="K122" s="126"/>
-      <c r="L122" s="127"/>
-      <c r="M122" s="127"/>
-      <c r="N122" s="127"/>
-      <c r="O122" s="127"/>
-      <c r="P122" s="125"/>
+      <c r="B122" s="158"/>
+      <c r="C122" s="158"/>
+      <c r="D122" s="121"/>
+      <c r="E122" s="121"/>
+      <c r="F122" s="121"/>
+      <c r="G122" s="121"/>
+      <c r="H122" s="120"/>
+      <c r="I122" s="120"/>
+      <c r="J122" s="121"/>
+      <c r="K122" s="125"/>
+      <c r="L122" s="126"/>
+      <c r="M122" s="126"/>
+      <c r="N122" s="126"/>
+      <c r="O122" s="126"/>
+      <c r="P122" s="124"/>
     </row>
     <row r="123" spans="1:16" s="20" customFormat="1" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="30">
         <v>16</v>
       </c>
-      <c r="B123" s="166"/>
-      <c r="C123" s="166"/>
+      <c r="B123" s="170"/>
+      <c r="C123" s="170"/>
       <c r="D123" s="65"/>
       <c r="E123" s="65"/>
       <c r="F123" s="65"/>
@@ -8508,27 +7981,27 @@
       <c r="P124" s="38"/>
     </row>
     <row r="125" spans="1:16" s="20" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="167"/>
-      <c r="B125" s="167"/>
-      <c r="C125" s="167"/>
-      <c r="D125" s="167"/>
-      <c r="E125" s="167"/>
-      <c r="F125" s="167"/>
-      <c r="G125" s="167"/>
-      <c r="H125" s="167"/>
-      <c r="I125" s="167"/>
-      <c r="J125" s="167"/>
-      <c r="K125" s="167"/>
-      <c r="L125" s="167"/>
-      <c r="M125" s="167"/>
-      <c r="N125" s="167"/>
-      <c r="O125" s="167"/>
-      <c r="P125" s="167"/>
+      <c r="A125" s="171"/>
+      <c r="B125" s="171"/>
+      <c r="C125" s="171"/>
+      <c r="D125" s="171"/>
+      <c r="E125" s="171"/>
+      <c r="F125" s="171"/>
+      <c r="G125" s="171"/>
+      <c r="H125" s="171"/>
+      <c r="I125" s="171"/>
+      <c r="J125" s="171"/>
+      <c r="K125" s="171"/>
+      <c r="L125" s="171"/>
+      <c r="M125" s="171"/>
+      <c r="N125" s="171"/>
+      <c r="O125" s="171"/>
+      <c r="P125" s="171"/>
     </row>
     <row r="126" spans="1:16" s="20" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="39"/>
-      <c r="B126" s="163"/>
-      <c r="C126" s="163"/>
+      <c r="B126" s="157"/>
+      <c r="C126" s="157"/>
       <c r="D126" s="40"/>
       <c r="E126" s="40"/>
       <c r="F126" s="40"/>
@@ -8545,8 +8018,8 @@
     </row>
     <row r="127" spans="1:16" s="20" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="39"/>
-      <c r="B127" s="163"/>
-      <c r="C127" s="163"/>
+      <c r="B127" s="157"/>
+      <c r="C127" s="157"/>
       <c r="D127" s="40"/>
       <c r="E127" s="40"/>
       <c r="F127" s="40"/>
@@ -8563,8 +8036,8 @@
     </row>
     <row r="128" spans="1:16" s="20" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="39"/>
-      <c r="B128" s="163"/>
-      <c r="C128" s="163"/>
+      <c r="B128" s="157"/>
+      <c r="C128" s="157"/>
       <c r="D128" s="40"/>
       <c r="E128" s="40"/>
       <c r="F128" s="40"/>
@@ -8581,8 +8054,8 @@
     </row>
     <row r="129" spans="1:16" s="20" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="39"/>
-      <c r="B129" s="163"/>
-      <c r="C129" s="163"/>
+      <c r="B129" s="157"/>
+      <c r="C129" s="157"/>
       <c r="D129" s="40"/>
       <c r="E129" s="40"/>
       <c r="F129" s="40"/>
@@ -8599,8 +8072,8 @@
     </row>
     <row r="130" spans="1:16" s="20" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="39"/>
-      <c r="B130" s="163"/>
-      <c r="C130" s="163"/>
+      <c r="B130" s="157"/>
+      <c r="C130" s="157"/>
       <c r="D130" s="40"/>
       <c r="E130" s="40"/>
       <c r="F130" s="40"/>
@@ -8617,8 +8090,8 @@
     </row>
     <row r="131" spans="1:16" s="20" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="39"/>
-      <c r="B131" s="176"/>
-      <c r="C131" s="176"/>
+      <c r="B131" s="156"/>
+      <c r="C131" s="156"/>
       <c r="D131" s="40"/>
       <c r="E131" s="40"/>
       <c r="F131" s="45"/>
@@ -8641,103 +8114,6 @@
     <row r="137" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="119">
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="A107:P107"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="A104:P104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="A2:P2"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A15:A20"/>
-    <mergeCell ref="A21:A25"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="A40:A42"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="A43:A47"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="A29:A34"/>
-    <mergeCell ref="A35:A39"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="A48:A52"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="A53:A55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A58:A60"/>
-    <mergeCell ref="A61:A63"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="A84:C84"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="A125:P125"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B87:C87"/>
     <mergeCell ref="M1:P1"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="B101:C101"/>
@@ -8760,6 +8136,103 @@
     <mergeCell ref="A77:C77"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="A67:P67"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="A125:P125"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="A29:A34"/>
+    <mergeCell ref="A35:A39"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A15:A20"/>
+    <mergeCell ref="A21:A25"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="A40:A42"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="A43:A47"/>
+    <mergeCell ref="A48:A52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="A107:P107"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="A104:P104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B119:C119"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <dataValidations count="2">
